--- a/EX2/CPa_effectivenes_pre_vs_post_calibration/CPa platt vs CPa uncalibrated - effectiveness difference.xlsx
+++ b/EX2/CPa_effectivenes_pre_vs_post_calibration/CPa platt vs CPa uncalibrated - effectiveness difference.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xhulj\Desktop\CPa\EX2\CPa_effectivenes_pre_vs_post_calibration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3380D894-F44E-4F90-A53D-3413C5194B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFE5D15E-46C0-4A25-8A84-7FAAD8950381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{84D757DF-780B-4A8F-90CA-835254FC4142}"/>
   </bookViews>
   <sheets>
-    <sheet name="CB" sheetId="1" r:id="rId1"/>
-    <sheet name="DJ" sheetId="2" r:id="rId2"/>
-    <sheet name="LA" sheetId="3" r:id="rId3"/>
+    <sheet name="CodeBERT4JIT" sheetId="1" r:id="rId1"/>
+    <sheet name="DeepJIT" sheetId="2" r:id="rId2"/>
+    <sheet name="LApredict" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="11">
   <si>
     <t>Precision</t>
   </si>
@@ -60,12 +60,24 @@
   <si>
     <t>Platt scaled</t>
   </si>
+  <si>
+    <t>Uncalibrated</t>
+  </si>
+  <si>
+    <t>(Platt-uncalibrated) Difference</t>
+  </si>
+  <si>
+    <t>Prediction posteriors</t>
+  </si>
+  <si>
+    <t>Difference (Platt-prediction posteriors)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -79,6 +91,28 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="8" tint="-0.249977111117893"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="8" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="8" tint="0.39997558519241921"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -102,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -110,6 +144,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -444,15 +486,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F71F0F4-893F-4527-974E-A5CA3584087B}">
-  <dimension ref="A1:Z17"/>
+  <dimension ref="A1:AQ17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="6" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="8.88671875" style="2"/>
     <col min="24" max="24" width="8.88671875" style="2"/>
+    <col min="38" max="38" width="8.88671875" style="2"/>
+    <col min="41" max="41" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>6</v>
       </c>
@@ -461,8 +505,35 @@
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="L1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="U1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="V1" s="5"/>
+      <c r="W1" s="5"/>
+      <c r="X1" s="5"/>
+      <c r="Y1" s="5"/>
+      <c r="Z1" s="5"/>
+      <c r="AD1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE1" s="4"/>
+      <c r="AF1" s="4"/>
+      <c r="AG1" s="4"/>
+      <c r="AH1" s="4"/>
+      <c r="AI1" s="4"/>
+      <c r="AL1" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -517,8 +588,44 @@
       <c r="Z2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AD2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AO2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>0.93258426966292129</v>
       </c>
@@ -579,8 +686,50 @@
         <f t="shared" si="0"/>
         <v>-0.18181818181818182</v>
       </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AD5" s="7">
+        <v>0.89647425028660721</v>
+      </c>
+      <c r="AE5" s="1">
+        <v>0.91269452633283421</v>
+      </c>
+      <c r="AF5" s="1">
+        <v>0.40988859384234111</v>
+      </c>
+      <c r="AG5" s="7">
+        <v>0.91462287869256131</v>
+      </c>
+      <c r="AH5" s="1">
+        <v>0.92816112779701487</v>
+      </c>
+      <c r="AI5" s="1">
+        <v>0.42304233970138955</v>
+      </c>
+      <c r="AL5" s="3">
+        <f>A5-AD5</f>
+        <v>3.6110019376314084E-2</v>
+      </c>
+      <c r="AM5" s="1">
+        <f t="shared" ref="AM5:AQ5" si="1">B5-AE5</f>
+        <v>8.7305473667165789E-2</v>
+      </c>
+      <c r="AN5" s="1">
+        <f t="shared" si="1"/>
+        <v>-0.40988859384234111</v>
+      </c>
+      <c r="AO5" s="3">
+        <f t="shared" si="1"/>
+        <v>-0.12958418565730767</v>
+      </c>
+      <c r="AP5" s="1">
+        <f t="shared" si="1"/>
+        <v>-0.13562640557479266</v>
+      </c>
+      <c r="AQ5" s="1">
+        <f t="shared" si="1"/>
+        <v>-0.42304233970138955</v>
+      </c>
+    </row>
+    <row r="6" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -592,8 +741,14 @@
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AL6" s="3"/>
+      <c r="AM6" s="1"/>
+      <c r="AN6" s="1"/>
+      <c r="AO6" s="3"/>
+      <c r="AP6" s="1"/>
+      <c r="AQ6" s="1"/>
+    </row>
+    <row r="7" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>0.89486356340288919</v>
       </c>
@@ -635,27 +790,69 @@
         <v>4.8635634028891817E-3</v>
       </c>
       <c r="V7" s="1">
-        <f t="shared" ref="V7:Z7" si="1">B7-M7</f>
+        <f t="shared" ref="V7:Z7" si="2">B7-M7</f>
         <v>1.824625660688961E-2</v>
       </c>
       <c r="W7" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-0.10005871990604816</v>
       </c>
       <c r="X7" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8.7274290627687989E-3</v>
       </c>
       <c r="Y7" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-1.4829607960796798E-3</v>
       </c>
       <c r="Z7" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-0.33333333333333337</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AD7" s="8">
+        <v>0.88569130016964803</v>
+      </c>
+      <c r="AE7" s="1">
+        <v>0.90648625838723873</v>
+      </c>
+      <c r="AF7" s="1">
+        <v>0.39627604911469866</v>
+      </c>
+      <c r="AG7" s="8">
+        <v>0.94438776389571188</v>
+      </c>
+      <c r="AH7" s="9">
+        <v>0.95520802465734078</v>
+      </c>
+      <c r="AI7" s="9">
+        <v>0.54836554643792279</v>
+      </c>
+      <c r="AL7" s="3">
+        <f>A7-AD7</f>
+        <v>9.1722632332411624E-3</v>
+      </c>
+      <c r="AM7" s="1">
+        <f t="shared" ref="AM7:AQ7" si="3">B7-AE7</f>
+        <v>9.2616880626214204E-2</v>
+      </c>
+      <c r="AN7" s="1">
+        <f t="shared" si="3"/>
+        <v>-0.3886424613284391</v>
+      </c>
+      <c r="AO7" s="3">
+        <f t="shared" si="3"/>
+        <v>1.433966516705687E-2</v>
+      </c>
+      <c r="AP7" s="1">
+        <f t="shared" si="3"/>
+        <v>1.1805864231548058E-2</v>
+      </c>
+      <c r="AQ7" s="1">
+        <f t="shared" si="3"/>
+        <v>-0.45745645552883185</v>
+      </c>
+    </row>
+    <row r="8" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -667,8 +864,14 @@
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AL8" s="3"/>
+      <c r="AM8" s="1"/>
+      <c r="AN8" s="1"/>
+      <c r="AO8" s="3"/>
+      <c r="AP8" s="1"/>
+      <c r="AQ8" s="1"/>
+    </row>
+    <row r="9" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>0.88620420888542484</v>
       </c>
@@ -710,27 +913,69 @@
         <v>1.6204208885424842E-2</v>
       </c>
       <c r="V9" s="1">
-        <f t="shared" ref="V9:Z9" si="2">B9-M9</f>
+        <f t="shared" ref="V9:Z9" si="4">B9-M9</f>
         <v>3.0576019072951599E-2</v>
       </c>
       <c r="W9" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-0.13522967872595049</v>
       </c>
       <c r="X9" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-2.3559759243335643E-3</v>
       </c>
       <c r="Y9" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-7.4921554655466016E-3</v>
       </c>
       <c r="Z9" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-0.39393939393939392</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AD9" s="7">
+        <v>0.87995955565741213</v>
+      </c>
+      <c r="AE9" s="1">
+        <v>0.90370861417927495</v>
+      </c>
+      <c r="AF9" s="1">
+        <v>0.39229369924488566</v>
+      </c>
+      <c r="AG9" s="7">
+        <v>0.9593259602906502</v>
+      </c>
+      <c r="AH9" s="1">
+        <v>0.96807912300555798</v>
+      </c>
+      <c r="AI9" s="1">
+        <v>0.63885868280607627</v>
+      </c>
+      <c r="AL9" s="3">
+        <f>A9-AD9</f>
+        <v>6.2446532280127087E-3</v>
+      </c>
+      <c r="AM9" s="1">
+        <f t="shared" ref="AM9:AQ9" si="5">B9-AE9</f>
+        <v>8.9279992306264044E-2</v>
+      </c>
+      <c r="AN9" s="1">
+        <f t="shared" si="5"/>
+        <v>-0.3641246851603786</v>
+      </c>
+      <c r="AO9" s="3">
+        <f t="shared" si="5"/>
+        <v>1.8318063785016214E-2</v>
+      </c>
+      <c r="AP9" s="1">
+        <f t="shared" si="5"/>
+        <v>1.5427821438886435E-2</v>
+      </c>
+      <c r="AQ9" s="1">
+        <f t="shared" si="5"/>
+        <v>-0.27522231916971263</v>
+      </c>
+    </row>
+    <row r="10" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -742,8 +987,14 @@
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AL10" s="3"/>
+      <c r="AM10" s="1"/>
+      <c r="AN10" s="1"/>
+      <c r="AO10" s="3"/>
+      <c r="AP10" s="1"/>
+      <c r="AQ10" s="1"/>
+    </row>
+    <row r="11" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -755,8 +1006,14 @@
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AL11" s="3"/>
+      <c r="AM11" s="1"/>
+      <c r="AN11" s="1"/>
+      <c r="AO11" s="3"/>
+      <c r="AP11" s="1"/>
+      <c r="AQ11" s="1"/>
+    </row>
+    <row r="12" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -768,8 +1025,14 @@
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AL12" s="3"/>
+      <c r="AM12" s="1"/>
+      <c r="AN12" s="1"/>
+      <c r="AO12" s="3"/>
+      <c r="AP12" s="1"/>
+      <c r="AQ12" s="1"/>
+    </row>
+    <row r="13" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>0.94512452511608269</v>
       </c>
@@ -811,27 +1074,69 @@
         <v>-4.8754748839172635E-3</v>
       </c>
       <c r="V13" s="1">
-        <f t="shared" ref="V13:Z13" si="3">B13-M13</f>
+        <f t="shared" ref="V13:Z13" si="6">B13-M13</f>
         <v>5.591458432171903E-3</v>
       </c>
       <c r="W13" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>-7.8514588859416451E-2</v>
       </c>
       <c r="X13" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>2.9177852348993283E-2</v>
       </c>
       <c r="Y13" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>2.2678327336631221E-2</v>
       </c>
       <c r="Z13" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>-0.25391849529780564</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AD13" s="7">
+        <v>0.93655789541389611</v>
+      </c>
+      <c r="AE13" s="1">
+        <v>0.94593988179961275</v>
+      </c>
+      <c r="AF13" s="1">
+        <v>0.38817437008475791</v>
+      </c>
+      <c r="AG13" s="7">
+        <v>0.95627927759889997</v>
+      </c>
+      <c r="AH13" s="1">
+        <v>0.96193628953336452</v>
+      </c>
+      <c r="AI13" s="1">
+        <v>0.4870498275662416</v>
+      </c>
+      <c r="AL13" s="3">
+        <f>A13-AD13</f>
+        <v>8.5666297021865789E-3</v>
+      </c>
+      <c r="AM13" s="1">
+        <f t="shared" ref="AM13:AQ13" si="7">B13-AE13</f>
+        <v>5.3613490241476991E-2</v>
+      </c>
+      <c r="AN13" s="1">
+        <f t="shared" si="7"/>
+        <v>-0.38048206239245019</v>
+      </c>
+      <c r="AO13" s="3">
+        <f t="shared" si="7"/>
+        <v>-1.7101425249906654E-2</v>
+      </c>
+      <c r="AP13" s="1">
+        <f t="shared" si="7"/>
+        <v>-1.9223568387618961E-2</v>
+      </c>
+      <c r="AQ13" s="1">
+        <f t="shared" si="7"/>
+        <v>-0.39614073665715066</v>
+      </c>
+    </row>
+    <row r="14" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -843,8 +1148,14 @@
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AL14" s="3"/>
+      <c r="AM14" s="1"/>
+      <c r="AN14" s="1"/>
+      <c r="AO14" s="3"/>
+      <c r="AP14" s="1"/>
+      <c r="AQ14" s="1"/>
+    </row>
+    <row r="15" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>0.93962722852512159</v>
       </c>
@@ -886,27 +1197,69 @@
         <v>9.627228525121545E-3</v>
       </c>
       <c r="V15" s="1">
-        <f t="shared" ref="V15:Z15" si="4">B15-M15</f>
+        <f t="shared" ref="V15:Z15" si="8">B15-M15</f>
         <v>1.8766731864829356E-2</v>
       </c>
       <c r="W15" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>-0.12372337321272249</v>
       </c>
       <c r="X15" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>-1.7265100671140954E-2</v>
       </c>
       <c r="Y15" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>-1.1980968952126081E-2</v>
       </c>
       <c r="Z15" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>-0.63322884012539182</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AD15" s="7">
+        <v>0.93150652982465443</v>
+      </c>
+      <c r="AE15" s="1">
+        <v>0.94370073256047027</v>
+      </c>
+      <c r="AF15" s="1">
+        <v>0.37053375707013869</v>
+      </c>
+      <c r="AG15" s="7">
+        <v>0.97090784893787263</v>
+      </c>
+      <c r="AH15" s="1">
+        <v>0.97540056429877242</v>
+      </c>
+      <c r="AI15" s="1">
+        <v>0.59981864189732481</v>
+      </c>
+      <c r="AL15" s="3">
+        <f>A15-AD15</f>
+        <v>8.120698700467166E-3</v>
+      </c>
+      <c r="AM15" s="1">
+        <f t="shared" ref="AM15:AQ15" si="9">B15-AE15</f>
+        <v>5.5868047085929073E-2</v>
+      </c>
+      <c r="AN15" s="1">
+        <f t="shared" si="9"/>
+        <v>-0.36382234767416555</v>
+      </c>
+      <c r="AO15" s="3">
+        <f t="shared" si="9"/>
+        <v>1.8270503909864066E-3</v>
+      </c>
+      <c r="AP15" s="1">
+        <f t="shared" si="9"/>
+        <v>1.0105561730051615E-3</v>
+      </c>
+      <c r="AQ15" s="1">
+        <f t="shared" si="9"/>
+        <v>-0.50890955098823387</v>
+      </c>
+    </row>
+    <row r="16" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -918,8 +1271,14 @@
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
       <c r="Q16" s="1"/>
-    </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AL16" s="3"/>
+      <c r="AM16" s="1"/>
+      <c r="AN16" s="1"/>
+      <c r="AO16" s="3"/>
+      <c r="AP16" s="1"/>
+      <c r="AQ16" s="1"/>
+    </row>
+    <row r="17" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>0.94989106753812635</v>
       </c>
@@ -961,29 +1320,74 @@
         <v>9.8910675381264079E-3</v>
       </c>
       <c r="V17" s="1">
-        <f t="shared" ref="V17:Z17" si="5">B17-M17</f>
+        <f t="shared" ref="V17:Z17" si="10">B17-M17</f>
         <v>8.2154267457781316E-3</v>
       </c>
       <c r="W17" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>-9.0163934426229511E-2</v>
       </c>
       <c r="X17" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>-1.5570469798657727E-2</v>
       </c>
       <c r="Y17" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>-1.5940458434415272E-2</v>
       </c>
       <c r="Z17" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>-0.37931034482758619</v>
       </c>
+      <c r="AD17" s="7">
+        <v>0.92835083465222401</v>
+      </c>
+      <c r="AE17" s="1">
+        <v>0.94235107793660389</v>
+      </c>
+      <c r="AF17" s="1">
+        <v>0.3620199063806267</v>
+      </c>
+      <c r="AG17" s="7">
+        <v>0.97845790673565081</v>
+      </c>
+      <c r="AH17" s="1">
+        <v>0.98208784389422799</v>
+      </c>
+      <c r="AI17" s="1">
+        <v>0.67982831522213616</v>
+      </c>
+      <c r="AL17" s="3">
+        <f>A17-AD17</f>
+        <v>2.1540232885902344E-2</v>
+      </c>
+      <c r="AM17" s="1">
+        <f t="shared" ref="AM17:AQ17" si="11">B17-AE17</f>
+        <v>5.7648922063396113E-2</v>
+      </c>
+      <c r="AN17" s="1">
+        <f t="shared" si="11"/>
+        <v>-0.3620199063806267</v>
+      </c>
+      <c r="AO17" s="3">
+        <f t="shared" si="11"/>
+        <v>-6.4028376534308484E-2</v>
+      </c>
+      <c r="AP17" s="1">
+        <f t="shared" si="11"/>
+        <v>-6.3806462259855645E-2</v>
+      </c>
+      <c r="AQ17" s="1">
+        <f t="shared" si="11"/>
+        <v>-0.67982831522213616</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="4">
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="L1:Q1"/>
+    <mergeCell ref="U1:Z1"/>
+    <mergeCell ref="AD1:AI1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
@@ -992,14 +1396,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{412150BC-5A87-49F3-A996-A83CB5E15361}">
-  <dimension ref="A1:Z17"/>
+  <dimension ref="A1:AQ17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="21" max="21" width="8.88671875" style="2"/>
     <col min="24" max="24" width="8.88671875" style="2"/>
+    <col min="38" max="38" width="8.88671875" style="2"/>
+    <col min="41" max="41" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>6</v>
       </c>
@@ -1008,8 +1414,35 @@
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="L1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="U1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="V1" s="5"/>
+      <c r="W1" s="5"/>
+      <c r="X1" s="5"/>
+      <c r="Y1" s="5"/>
+      <c r="Z1" s="5"/>
+      <c r="AD1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE1" s="4"/>
+      <c r="AF1" s="4"/>
+      <c r="AG1" s="4"/>
+      <c r="AH1" s="4"/>
+      <c r="AI1" s="4"/>
+      <c r="AL1" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1064,8 +1497,44 @@
       <c r="Z2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AD2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AO2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>0.92928176795580109</v>
       </c>
@@ -1126,8 +1595,50 @@
         <f t="shared" si="0"/>
         <v>-0.19565217391304349</v>
       </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AL5" s="3">
+        <f>A5-AD5</f>
+        <v>0.92928176795580109</v>
+      </c>
+      <c r="AM5" s="1">
+        <f t="shared" ref="AM5:AQ5" si="1">B5-AE5</f>
+        <v>1</v>
+      </c>
+      <c r="AN5" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO5" s="3">
+        <f t="shared" si="1"/>
+        <v>0.72003424657534243</v>
+      </c>
+      <c r="AP5" s="1">
+        <f t="shared" si="1"/>
+        <v>0.72003424657534243</v>
+      </c>
+      <c r="AQ5" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
@@ -1136,8 +1647,14 @@
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AL6" s="3"/>
+      <c r="AM6" s="1"/>
+      <c r="AN6" s="1"/>
+      <c r="AO6" s="3"/>
+      <c r="AP6" s="1"/>
+      <c r="AQ6" s="1"/>
+    </row>
+    <row r="7" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>0.88952536824877249</v>
       </c>
@@ -1179,11 +1696,11 @@
         <v>0.12952536824877248</v>
       </c>
       <c r="V7" s="1">
-        <f t="shared" ref="V7:Z7" si="1">B7-M7</f>
+        <f t="shared" ref="V7:Z7" si="2">B7-M7</f>
         <v>0.24460431654676262</v>
       </c>
       <c r="W7" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-0.86440677966101698</v>
       </c>
       <c r="X7" s="3">
@@ -1191,15 +1708,57 @@
         <v>0.32447307875390063</v>
       </c>
       <c r="Y7" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.27337368962634245</v>
       </c>
       <c r="Z7" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-0.36956521739130432</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AL7" s="3">
+        <f>A7-AD7</f>
+        <v>0.88952536824877249</v>
+      </c>
+      <c r="AM7" s="1">
+        <f t="shared" ref="AM7:AQ7" si="3">B7-AE7</f>
+        <v>1</v>
+      </c>
+      <c r="AN7" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AO7" s="3">
+        <f t="shared" si="3"/>
+        <v>0.93065068493150682</v>
+      </c>
+      <c r="AP7" s="1">
+        <f t="shared" si="3"/>
+        <v>0.93065068493150682</v>
+      </c>
+      <c r="AQ7" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -1208,8 +1767,14 @@
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AL8" s="3"/>
+      <c r="AM8" s="1"/>
+      <c r="AN8" s="1"/>
+      <c r="AO8" s="3"/>
+      <c r="AP8" s="1"/>
+      <c r="AQ8" s="1"/>
+    </row>
+    <row r="9" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>0.88452474469756481</v>
       </c>
@@ -1251,11 +1816,11 @@
         <v>0.18452474469756486</v>
       </c>
       <c r="V9" s="1">
-        <f t="shared" ref="V9:Z9" si="2">B9-M9</f>
+        <f t="shared" ref="V9:Z9" si="4">B9-M9</f>
         <v>0.32511556240369799</v>
       </c>
       <c r="W9" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-0.89123456790123456</v>
       </c>
       <c r="X9" s="3">
@@ -1263,15 +1828,57 @@
         <v>0.30638343823275327</v>
       </c>
       <c r="Y9" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.27859508650073961</v>
       </c>
       <c r="Z9" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-0.52898550724637683</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AD9" s="7">
+        <v>0.67219648110612795</v>
+      </c>
+      <c r="AE9" s="1">
+        <v>0.99192400189629626</v>
+      </c>
+      <c r="AF9" s="1">
+        <v>0.25876068380073264</v>
+      </c>
+      <c r="AG9" s="7">
+        <v>3.7777172854017799E-2</v>
+      </c>
+      <c r="AH9" s="1">
+        <v>3.9524430257438035E-2</v>
+      </c>
+      <c r="AI9" s="1">
+        <v>2.6845000949617025E-2</v>
+      </c>
+      <c r="AL9" s="3">
+        <f>A9-AD9</f>
+        <v>0.21232826359143686</v>
+      </c>
+      <c r="AM9" s="1">
+        <f t="shared" ref="AM9:AQ9" si="5">B9-AE9</f>
+        <v>8.0759981037037409E-3</v>
+      </c>
+      <c r="AN9" s="1">
+        <f t="shared" si="5"/>
+        <v>-0.24876068380073263</v>
+      </c>
+      <c r="AO9" s="3">
+        <f t="shared" si="5"/>
+        <v>0.92626392303639316</v>
+      </c>
+      <c r="AP9" s="1">
+        <f t="shared" si="5"/>
+        <v>0.92451666563297297</v>
+      </c>
+      <c r="AQ9" s="1">
+        <f t="shared" si="5"/>
+        <v>-2.6845000949617025E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -1280,8 +1887,14 @@
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AL10" s="3"/>
+      <c r="AM10" s="1"/>
+      <c r="AN10" s="1"/>
+      <c r="AO10" s="3"/>
+      <c r="AP10" s="1"/>
+      <c r="AQ10" s="1"/>
+    </row>
+    <row r="11" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -1290,8 +1903,14 @@
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AL11" s="3"/>
+      <c r="AM11" s="1"/>
+      <c r="AN11" s="1"/>
+      <c r="AO11" s="3"/>
+      <c r="AP11" s="1"/>
+      <c r="AQ11" s="1"/>
+    </row>
+    <row r="12" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -1300,8 +1919,14 @@
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AL12" s="3"/>
+      <c r="AM12" s="1"/>
+      <c r="AN12" s="1"/>
+      <c r="AO12" s="3"/>
+      <c r="AP12" s="1"/>
+      <c r="AQ12" s="1"/>
+    </row>
+    <row r="13" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>0.94134775374376045</v>
       </c>
@@ -1343,11 +1968,11 @@
         <v>0.1313477537437604</v>
       </c>
       <c r="V13" s="1">
-        <f t="shared" ref="V13:Z13" si="3">B13-M13</f>
+        <f t="shared" ref="V13:Z13" si="6">B13-M13</f>
         <v>0.18691588785046731</v>
       </c>
       <c r="W13" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>-0.87755102040816324</v>
       </c>
       <c r="X13" s="3">
@@ -1355,15 +1980,57 @@
         <v>0.63844928751047769</v>
       </c>
       <c r="Y13" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.64818273987733921</v>
       </c>
       <c r="Z13" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>-0.34677419354838712</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AD13" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="AE13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="AG13" s="7">
+        <v>1.5938580000000001E-4</v>
+      </c>
+      <c r="AH13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="1">
+        <v>2.486912E-3</v>
+      </c>
+      <c r="AL13" s="3">
+        <f>A13-AD13</f>
+        <v>0.7413477537437605</v>
+      </c>
+      <c r="AM13" s="1">
+        <f t="shared" ref="AM13:AQ13" si="7">B13-AE13</f>
+        <v>1</v>
+      </c>
+      <c r="AN13" s="1">
+        <f t="shared" si="7"/>
+        <v>-0.2</v>
+      </c>
+      <c r="AO13" s="3">
+        <f t="shared" si="7"/>
+        <v>0.94828990171047778</v>
+      </c>
+      <c r="AP13" s="1">
+        <f t="shared" si="7"/>
+        <v>0.95044099118017644</v>
+      </c>
+      <c r="AQ13" s="1">
+        <f t="shared" si="7"/>
+        <v>-2.486912E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
@@ -1372,8 +2039,14 @@
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AL14" s="3"/>
+      <c r="AM14" s="1"/>
+      <c r="AN14" s="1"/>
+      <c r="AO14" s="3"/>
+      <c r="AP14" s="1"/>
+      <c r="AQ14" s="1"/>
+    </row>
+    <row r="15" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>0.93724696356275305</v>
       </c>
@@ -1415,11 +2088,11 @@
         <v>0.13724696356275301</v>
       </c>
       <c r="V15" s="1">
-        <f t="shared" ref="V15:Z15" si="4">B15-M15</f>
+        <f t="shared" ref="V15:Z15" si="8">B15-M15</f>
         <v>0.19184652278177461</v>
       </c>
       <c r="W15" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>-0.77419354838709675</v>
       </c>
       <c r="X15" s="3">
@@ -1427,15 +2100,57 @@
         <v>0.3802430846605197</v>
       </c>
       <c r="Y15" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0.38687233203801474</v>
       </c>
       <c r="Z15" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>-0.58064516129032262</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AD15" s="7">
+        <v>0.61559422054545454</v>
+      </c>
+      <c r="AE15" s="1">
+        <v>1</v>
+      </c>
+      <c r="AF15" s="1">
+        <v>0.30664508818181824</v>
+      </c>
+      <c r="AG15" s="7">
+        <v>3.2510241000000002E-2</v>
+      </c>
+      <c r="AH15" s="1">
+        <v>2.5630543545454545E-2</v>
+      </c>
+      <c r="AI15" s="1">
+        <v>0.12948781645454546</v>
+      </c>
+      <c r="AL15" s="3">
+        <f>A15-AD15</f>
+        <v>0.32165274301729851</v>
+      </c>
+      <c r="AM15" s="1">
+        <f t="shared" ref="AM15:AQ15" si="9">B15-AE15</f>
+        <v>0</v>
+      </c>
+      <c r="AN15" s="1">
+        <f t="shared" si="9"/>
+        <v>-0.30664508818181824</v>
+      </c>
+      <c r="AO15" s="3">
+        <f t="shared" si="9"/>
+        <v>0.93773284366051968</v>
+      </c>
+      <c r="AP15" s="1">
+        <f t="shared" si="9"/>
+        <v>0.94665001084345768</v>
+      </c>
+      <c r="AQ15" s="1">
+        <f t="shared" si="9"/>
+        <v>-0.12948781645454546</v>
+      </c>
+    </row>
+    <row r="16" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -1444,8 +2159,14 @@
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
       <c r="Q16" s="1"/>
-    </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AL16" s="3"/>
+      <c r="AM16" s="1"/>
+      <c r="AN16" s="1"/>
+      <c r="AO16" s="3"/>
+      <c r="AP16" s="1"/>
+      <c r="AQ16" s="1"/>
+    </row>
+    <row r="17" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>0.94684528954191871</v>
       </c>
@@ -1487,11 +2208,11 @@
         <v>0.16684528954191868</v>
       </c>
       <c r="V17" s="1">
-        <f t="shared" ref="V17:Z17" si="5">B17-M17</f>
+        <f t="shared" ref="V17:Z17" si="10">B17-M17</f>
         <v>0.21884317233154438</v>
       </c>
       <c r="W17" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>-0.72180451127819545</v>
       </c>
       <c r="X17" s="3">
@@ -1499,17 +2220,62 @@
         <v>0.15827326068734282</v>
       </c>
       <c r="Y17" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>0.16166077373299081</v>
       </c>
       <c r="Z17" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>-0.77419354838709675</v>
       </c>
+      <c r="AD17" s="7">
+        <v>0.75477757894000008</v>
+      </c>
+      <c r="AE17" s="1">
+        <v>0.99424652603999975</v>
+      </c>
+      <c r="AF17" s="1">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AG17" s="7">
+        <v>0.14306746273999998</v>
+      </c>
+      <c r="AH17" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="AI17" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="AL17" s="3">
+        <f>A17-AD17</f>
+        <v>0.19206771060191863</v>
+      </c>
+      <c r="AM17" s="1">
+        <f t="shared" ref="AM17:AQ17" si="11">B17-AE17</f>
+        <v>5.7534739600002549E-3</v>
+      </c>
+      <c r="AN17" s="1">
+        <f t="shared" si="11"/>
+        <v>-0.28000000000000003</v>
+      </c>
+      <c r="AO17" s="3">
+        <f t="shared" si="11"/>
+        <v>0.77520579794734279</v>
+      </c>
+      <c r="AP17" s="1">
+        <f t="shared" si="11"/>
+        <v>0.79020159596808059</v>
+      </c>
+      <c r="AQ17" s="1">
+        <f t="shared" si="11"/>
+        <v>-0.26</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="4">
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="L1:Q1"/>
+    <mergeCell ref="U1:Z1"/>
+    <mergeCell ref="AD1:AI1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1517,14 +2283,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5E3B8BC-A264-4B08-80A2-0E1FBB2077B5}">
-  <dimension ref="A1:AA17"/>
+  <dimension ref="A1:AQ17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="21" max="21" width="8.88671875" style="2"/>
     <col min="24" max="24" width="8.88671875" style="2"/>
+    <col min="38" max="38" width="8.88671875" style="2"/>
+    <col min="41" max="41" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>6</v>
       </c>
@@ -1533,15 +2301,41 @@
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="4"/>
-      <c r="W1" s="4"/>
-      <c r="X1" s="4"/>
-      <c r="Y1" s="4"/>
-      <c r="Z1" s="4"/>
-      <c r="AA1" s="4"/>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="L1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="U1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="V1" s="5"/>
+      <c r="W1" s="5"/>
+      <c r="X1" s="5"/>
+      <c r="Y1" s="5"/>
+      <c r="Z1" s="5"/>
+      <c r="AA1" s="6"/>
+      <c r="AD1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE1" s="4"/>
+      <c r="AF1" s="4"/>
+      <c r="AG1" s="4"/>
+      <c r="AH1" s="4"/>
+      <c r="AI1" s="4"/>
+      <c r="AL1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM1" s="5"/>
+      <c r="AN1" s="5"/>
+      <c r="AO1" s="5"/>
+      <c r="AP1" s="5"/>
+      <c r="AQ1" s="5"/>
+    </row>
+    <row r="2" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1596,8 +2390,44 @@
       <c r="Z2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AD2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AO2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>0.91072400653238972</v>
       </c>
@@ -1658,8 +2488,50 @@
         <f t="shared" si="0"/>
         <v>8.4097280096976923E-3</v>
       </c>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AD5" s="10">
+        <v>0.94594594594594583</v>
+      </c>
+      <c r="AE5" s="1">
+        <v>0.95402298850574696</v>
+      </c>
+      <c r="AF5" s="1">
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="AG5" s="10">
+        <v>4.720798489344484E-2</v>
+      </c>
+      <c r="AH5" s="1">
+        <v>4.7347404449515122E-2</v>
+      </c>
+      <c r="AI5" s="1">
+        <v>4.4776119402985079E-2</v>
+      </c>
+      <c r="AL5" s="3">
+        <f>A5-AD5</f>
+        <v>-3.5221939413556114E-2</v>
+      </c>
+      <c r="AM5" s="1">
+        <f t="shared" ref="AM5:AQ5" si="1">B5-AE5</f>
+        <v>3.8708689265300911E-2</v>
+      </c>
+      <c r="AN5" s="1">
+        <f t="shared" si="1"/>
+        <v>-0.6353861192570871</v>
+      </c>
+      <c r="AO5" s="3">
+        <f t="shared" si="1"/>
+        <v>0.40483200429866539</v>
+      </c>
+      <c r="AP5" s="1">
+        <f t="shared" si="1"/>
+        <v>0.42040373710299628</v>
+      </c>
+      <c r="AQ5" s="1">
+        <f t="shared" si="1"/>
+        <v>0.12781271308432457</v>
+      </c>
+    </row>
+    <row r="6" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -1672,7 +2544,7 @@
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>0.89054545454545453</v>
       </c>
@@ -1714,27 +2586,69 @@
         <v>5.4545454545451566E-4</v>
       </c>
       <c r="V7" s="1">
-        <f t="shared" ref="V7:Z7" si="1">B7-M7</f>
+        <f t="shared" ref="V7:Z7" si="2">B7-M7</f>
         <v>-4.963167047696837E-4</v>
       </c>
       <c r="W7" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.4925373134328374E-2</v>
       </c>
       <c r="X7" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-8.2869494731153681E-3</v>
       </c>
       <c r="Y7" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-6.1707653155581577E-3</v>
       </c>
       <c r="Z7" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.0633633861151088E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AD7" s="10">
+        <v>0.92405063291139222</v>
+      </c>
+      <c r="AE7" s="1">
+        <v>0.93013100436681218</v>
+      </c>
+      <c r="AF7" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="AG7" s="10">
+        <v>0.11815484219045048</v>
+      </c>
+      <c r="AH7" s="1">
+        <v>0.1215059897318882</v>
+      </c>
+      <c r="AI7" s="1">
+        <v>5.9701492537313432E-2</v>
+      </c>
+      <c r="AL7" s="3">
+        <f>A7-AD7</f>
+        <v>-3.3505178365937693E-2</v>
+      </c>
+      <c r="AM7" s="1">
+        <f t="shared" ref="AM7:AQ7" si="3">B7-AE7</f>
+        <v>6.0345186109378335E-2</v>
+      </c>
+      <c r="AN7" s="1">
+        <f t="shared" si="3"/>
+        <v>-0.57985074626865674</v>
+      </c>
+      <c r="AO7" s="3">
+        <f t="shared" si="3"/>
+        <v>0.5435582083364342</v>
+      </c>
+      <c r="AP7" s="1">
+        <f t="shared" si="3"/>
+        <v>0.56114241209459581</v>
+      </c>
+      <c r="AQ7" s="1">
+        <f t="shared" si="3"/>
+        <v>0.22963860898552918</v>
+      </c>
+    </row>
+    <row r="8" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -1747,7 +2661,7 @@
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>0.86423274386765547</v>
       </c>
@@ -1789,27 +2703,69 @@
         <v>4.2327438676554863E-3</v>
       </c>
       <c r="V9" s="1">
-        <f t="shared" ref="V9:Z9" si="2">B9-M9</f>
+        <f t="shared" ref="V9:Z9" si="4">B9-M9</f>
         <v>-7.266452612149088E-4</v>
       </c>
       <c r="W9" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-8.228761024594522E-3</v>
       </c>
       <c r="X9" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-1.3023507160226933E-3</v>
       </c>
       <c r="Y9" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-3.5138718491718457E-3</v>
       </c>
       <c r="Z9" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-2.1163219435815894E-2</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AD9" s="10">
+        <v>0.93081081081081074</v>
+      </c>
+      <c r="AE9" s="1">
+        <v>0.93444444444444463</v>
+      </c>
+      <c r="AF9" s="1">
+        <v>0.79999999999999993</v>
+      </c>
+      <c r="AG9" s="10">
+        <v>0.23226328567574855</v>
+      </c>
+      <c r="AH9" s="1">
+        <v>0.23987450085567599</v>
+      </c>
+      <c r="AI9" s="1">
+        <v>9.950248756218906E-2</v>
+      </c>
+      <c r="AL9" s="3">
+        <f>A9-AD9</f>
+        <v>-6.6578066943155267E-2</v>
+      </c>
+      <c r="AM9" s="1">
+        <f t="shared" ref="AM9:AQ9" si="5">B9-AE9</f>
+        <v>5.0500353146722965E-2</v>
+      </c>
+      <c r="AN9" s="1">
+        <f t="shared" si="5"/>
+        <v>-0.63365570599613141</v>
+      </c>
+      <c r="AO9" s="3">
+        <f t="shared" si="5"/>
+        <v>0.58643436360822876</v>
+      </c>
+      <c r="AP9" s="1">
+        <f t="shared" si="5"/>
+        <v>0.60030814754615047</v>
+      </c>
+      <c r="AQ9" s="1">
+        <f t="shared" si="5"/>
+        <v>0.33704573578806474</v>
+      </c>
+    </row>
+    <row r="10" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -1822,7 +2778,7 @@
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -1835,7 +2791,7 @@
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -1848,7 +2804,7 @@
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>0.90832696715049654</v>
       </c>
@@ -1890,27 +2846,69 @@
         <v>-1.6730328495034863E-3</v>
       </c>
       <c r="V13" s="1">
-        <f t="shared" ref="V13:Z13" si="3">B13-M13</f>
+        <f t="shared" ref="V13:Z13" si="6">B13-M13</f>
         <v>-4.4670180036232576E-4</v>
       </c>
       <c r="W13" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>4.3682008368200829E-3</v>
       </c>
       <c r="X13" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>-1.8439716312056764E-2</v>
       </c>
       <c r="Y13" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>-1.977279292016243E-2</v>
       </c>
       <c r="Z13" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>4.6956521739130432E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AD13" s="10">
+        <v>0.90196078431372562</v>
+      </c>
+      <c r="AE13" s="1">
+        <v>0.92000000000000015</v>
+      </c>
+      <c r="AF13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="10">
+        <v>1.1352517345668032E-2</v>
+      </c>
+      <c r="AH13" s="1">
+        <v>1.1489936674755636E-2</v>
+      </c>
+      <c r="AI13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="3">
+        <f>A13-AD13</f>
+        <v>6.3661828367709283E-3</v>
+      </c>
+      <c r="AM13" s="1">
+        <f t="shared" ref="AM13:AQ13" si="7">B13-AE13</f>
+        <v>7.873896595208052E-2</v>
+      </c>
+      <c r="AN13" s="1">
+        <f t="shared" si="7"/>
+        <v>8.368200836820083E-3</v>
+      </c>
+      <c r="AO13" s="3">
+        <f t="shared" si="7"/>
+        <v>0.57020776634227521</v>
+      </c>
+      <c r="AP13" s="1">
+        <f t="shared" si="7"/>
+        <v>0.57272447198027265</v>
+      </c>
+      <c r="AQ13" s="1">
+        <f t="shared" si="7"/>
+        <v>8.6956521739130432E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1923,7 +2921,7 @@
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>0.87935323383084574</v>
       </c>
@@ -1965,27 +2963,69 @@
         <v>-6.4676616915426699E-4</v>
       </c>
       <c r="V15" s="1">
-        <f t="shared" ref="V15:Z15" si="4">B15-M15</f>
+        <f t="shared" ref="V15:Z15" si="8">B15-M15</f>
         <v>-9.1432896602849922E-6</v>
       </c>
       <c r="W15" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1.2597896151342672E-4</v>
       </c>
       <c r="X15" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>-5.4854487649792505E-3</v>
       </c>
       <c r="Y15" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>-6.515344959378111E-3</v>
       </c>
       <c r="Z15" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1.739130434782607E-2</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AD15" s="10">
+        <v>0.92531120331950212</v>
+      </c>
+      <c r="AE15" s="1">
+        <v>0.92640949554896146</v>
+      </c>
+      <c r="AF15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="10">
+        <v>0.38524520818669117</v>
+      </c>
+      <c r="AH15" s="1">
+        <v>0.38990850324551196</v>
+      </c>
+      <c r="AI15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="3">
+        <f>A15-AD15</f>
+        <v>-4.5957969488656381E-2</v>
+      </c>
+      <c r="AM15" s="1">
+        <f t="shared" ref="AM15:AQ15" si="9">B15-AE15</f>
+        <v>7.2176077294037078E-2</v>
+      </c>
+      <c r="AN15" s="1">
+        <f t="shared" si="9"/>
+        <v>1.0309278350515464E-2</v>
+      </c>
+      <c r="AO15" s="3">
+        <f t="shared" si="9"/>
+        <v>0.47926934304832958</v>
+      </c>
+      <c r="AP15" s="1">
+        <f t="shared" si="9"/>
+        <v>0.47805313924280868</v>
+      </c>
+      <c r="AQ15" s="1">
+        <f t="shared" si="9"/>
+        <v>0.21739130434782608</v>
+      </c>
+    </row>
+    <row r="16" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1998,7 +3038,7 @@
       <c r="P16" s="1"/>
       <c r="Q16" s="1"/>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>0.85771926098959439</v>
       </c>
@@ -2040,30 +3080,75 @@
         <v>-2.2807390104055969E-3</v>
       </c>
       <c r="V17" s="1">
-        <f t="shared" ref="V17:Z17" si="5">B17-M17</f>
+        <f t="shared" ref="V17:Z17" si="10">B17-M17</f>
         <v>-1.4796198488700174E-3</v>
       </c>
       <c r="W17" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>4.3769160196021374E-3</v>
       </c>
       <c r="X17" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>-2.2279285888969769E-3</v>
       </c>
       <c r="Y17" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>-4.8111193865063573E-4</v>
       </c>
       <c r="Z17" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>0.18260869565217397</v>
       </c>
+      <c r="AD17" s="10">
+        <v>0.9015862738750402</v>
+      </c>
+      <c r="AE17" s="1">
+        <v>0.90243111831442469</v>
+      </c>
+      <c r="AF17" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="AG17" s="10">
+        <v>0.68732088712359718</v>
+      </c>
+      <c r="AH17" s="1">
+        <v>0.6953909500547758</v>
+      </c>
+      <c r="AI17" s="1">
+        <v>2.1647058823529408E-2</v>
+      </c>
+      <c r="AL17" s="3">
+        <f>A17-AD17</f>
+        <v>-4.3867012885445811E-2</v>
+      </c>
+      <c r="AM17" s="1">
+        <f t="shared" ref="AM17:AQ17" si="11">B17-AE17</f>
+        <v>9.311233303491917E-2</v>
+      </c>
+      <c r="AN17" s="1">
+        <f t="shared" si="11"/>
+        <v>-0.22313432835820896</v>
+      </c>
+      <c r="AO17" s="3">
+        <f t="shared" si="11"/>
+        <v>0.30045118428750583</v>
+      </c>
+      <c r="AP17" s="1">
+        <f t="shared" si="11"/>
+        <v>0.29329850162951232</v>
+      </c>
+      <c r="AQ17" s="1">
+        <f t="shared" si="11"/>
+        <v>0.76096163682864448</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="5">
+    <mergeCell ref="AL1:AQ1"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="U1:AA1"/>
+    <mergeCell ref="L1:Q1"/>
+    <mergeCell ref="U1:Z1"/>
+    <mergeCell ref="AD1:AI1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/EX2/CPa_effectivenes_pre_vs_post_calibration/CPa platt vs CPa uncalibrated - effectiveness difference.xlsx
+++ b/EX2/CPa_effectivenes_pre_vs_post_calibration/CPa platt vs CPa uncalibrated - effectiveness difference.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xhulj\Desktop\CPa\EX2\CPa_effectivenes_pre_vs_post_calibration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFE5D15E-46C0-4A25-8A84-7FAAD8950381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1566772D-06BF-4776-B362-7291F14B1586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{84D757DF-780B-4A8F-90CA-835254FC4142}"/>
   </bookViews>
@@ -136,22 +136,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -497,38 +496,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="L1" s="4" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="L1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="U1" s="5" t="s">
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="U1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="V1" s="5"/>
-      <c r="W1" s="5"/>
-      <c r="X1" s="5"/>
-      <c r="Y1" s="5"/>
-      <c r="Z1" s="5"/>
-      <c r="AD1" s="4" t="s">
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="9"/>
+      <c r="Z1" s="9"/>
+      <c r="AD1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="AE1" s="4"/>
-      <c r="AF1" s="4"/>
-      <c r="AG1" s="4"/>
-      <c r="AH1" s="4"/>
-      <c r="AI1" s="4"/>
+      <c r="AE1" s="8"/>
+      <c r="AF1" s="8"/>
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="8"/>
+      <c r="AI1" s="8"/>
       <c r="AL1" s="2" t="s">
         <v>10</v>
       </c>
@@ -630,7 +629,7 @@
         <v>0.93258426966292129</v>
       </c>
       <c r="B5" s="1">
-        <v>1</v>
+        <v>0.93353783231083842</v>
       </c>
       <c r="C5" s="1">
         <v>0</v>
@@ -648,10 +647,10 @@
         <v>0.93</v>
       </c>
       <c r="M5" s="1">
-        <v>0.99332591768631817</v>
+        <v>0.93507853403141361</v>
       </c>
       <c r="N5" s="1">
-        <v>8.8235294117647065E-2</v>
+        <v>0.5</v>
       </c>
       <c r="O5" s="1">
         <v>0.79</v>
@@ -668,11 +667,11 @@
       </c>
       <c r="V5" s="1">
         <f t="shared" ref="V5:Z5" si="0">B5-M5</f>
-        <v>6.6740823136818284E-3</v>
+        <v>-1.5407017205751883E-3</v>
       </c>
       <c r="W5" s="1">
         <f t="shared" si="0"/>
-        <v>-8.8235294117647065E-2</v>
+        <v>-0.5</v>
       </c>
       <c r="X5" s="3">
         <f t="shared" si="0"/>
@@ -686,7 +685,7 @@
         <f t="shared" si="0"/>
         <v>-0.18181818181818182</v>
       </c>
-      <c r="AD5" s="7">
+      <c r="AD5" s="4">
         <v>0.89647425028660721</v>
       </c>
       <c r="AE5" s="1">
@@ -695,7 +694,7 @@
       <c r="AF5" s="1">
         <v>0.40988859384234111</v>
       </c>
-      <c r="AG5" s="7">
+      <c r="AG5" s="4">
         <v>0.91462287869256131</v>
       </c>
       <c r="AH5" s="1">
@@ -710,7 +709,7 @@
       </c>
       <c r="AM5" s="1">
         <f t="shared" ref="AM5:AQ5" si="1">B5-AE5</f>
-        <v>8.7305473667165789E-2</v>
+        <v>2.0843305978004212E-2</v>
       </c>
       <c r="AN5" s="1">
         <f t="shared" si="1"/>
@@ -753,28 +752,28 @@
         <v>0.89486356340288919</v>
       </c>
       <c r="B7" s="1">
-        <v>0.99910313901345293</v>
+        <v>0.89254210104250198</v>
       </c>
       <c r="C7" s="1">
-        <v>7.6335877862595417E-3</v>
+        <v>0.2638888888888889</v>
       </c>
       <c r="D7" s="1">
         <v>0.95872742906276875</v>
       </c>
       <c r="E7" s="1">
-        <v>0.96701388888888884</v>
+        <v>0.96</v>
       </c>
       <c r="F7" s="1">
-        <v>9.0909090909090912E-2</v>
+        <v>0.17272727272727273</v>
       </c>
       <c r="L7">
         <v>0.89</v>
       </c>
       <c r="M7" s="1">
-        <v>0.98085688240656332</v>
+        <v>0.9034424853064652</v>
       </c>
       <c r="N7" s="1">
-        <v>0.1076923076923077</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="O7" s="1">
         <v>0.95</v>
@@ -783,7 +782,7 @@
         <v>0.96849684968496852</v>
       </c>
       <c r="Q7" s="1">
-        <v>0.42424242424242425</v>
+        <v>0.45</v>
       </c>
       <c r="U7" s="3">
         <f>A7-L7</f>
@@ -791,11 +790,11 @@
       </c>
       <c r="V7" s="1">
         <f t="shared" ref="V7:Z7" si="2">B7-M7</f>
-        <v>1.824625660688961E-2</v>
+        <v>-1.0900384263963225E-2</v>
       </c>
       <c r="W7" s="1">
         <f t="shared" si="2"/>
-        <v>-0.10005871990604816</v>
+        <v>-0.15277777777777779</v>
       </c>
       <c r="X7" s="3">
         <f t="shared" si="2"/>
@@ -803,13 +802,13 @@
       </c>
       <c r="Y7" s="1">
         <f t="shared" si="2"/>
-        <v>-1.4829607960796798E-3</v>
+        <v>-8.4968496849685549E-3</v>
       </c>
       <c r="Z7" s="1">
         <f t="shared" si="2"/>
-        <v>-0.33333333333333337</v>
-      </c>
-      <c r="AD7" s="8">
+        <v>-0.27727272727272728</v>
+      </c>
+      <c r="AD7" s="5">
         <v>0.88569130016964803</v>
       </c>
       <c r="AE7" s="1">
@@ -818,13 +817,13 @@
       <c r="AF7" s="1">
         <v>0.39627604911469866</v>
       </c>
-      <c r="AG7" s="8">
+      <c r="AG7" s="5">
         <v>0.94438776389571188</v>
       </c>
-      <c r="AH7" s="9">
+      <c r="AH7" s="6">
         <v>0.95520802465734078</v>
       </c>
-      <c r="AI7" s="9">
+      <c r="AI7" s="6">
         <v>0.54836554643792279</v>
       </c>
       <c r="AL7" s="3">
@@ -833,11 +832,11 @@
       </c>
       <c r="AM7" s="1">
         <f t="shared" ref="AM7:AQ7" si="3">B7-AE7</f>
-        <v>9.2616880626214204E-2</v>
+        <v>-1.3944157344736752E-2</v>
       </c>
       <c r="AN7" s="1">
         <f t="shared" si="3"/>
-        <v>-0.3886424613284391</v>
+        <v>-0.13238716022580976</v>
       </c>
       <c r="AO7" s="3">
         <f t="shared" si="3"/>
@@ -845,11 +844,11 @@
       </c>
       <c r="AP7" s="1">
         <f t="shared" si="3"/>
-        <v>1.1805864231548058E-2</v>
+        <v>4.7919753426591827E-3</v>
       </c>
       <c r="AQ7" s="1">
         <f t="shared" si="3"/>
-        <v>-0.45745645552883185</v>
+        <v>-0.37563827371065006</v>
       </c>
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.3">
@@ -876,28 +875,28 @@
         <v>0.88620420888542484</v>
       </c>
       <c r="B9" s="1">
-        <v>0.99298860648553899</v>
+        <v>0.89274447949526814</v>
       </c>
       <c r="C9" s="1">
-        <v>2.8169014084507043E-2</v>
+        <v>0.25581395348837205</v>
       </c>
       <c r="D9" s="1">
         <v>0.97764402407566642</v>
       </c>
       <c r="E9" s="1">
-        <v>0.98350694444444442</v>
+        <v>0.98263888888888884</v>
       </c>
       <c r="F9" s="1">
-        <v>0.36363636363636365</v>
+        <v>0.3</v>
       </c>
       <c r="L9">
         <v>0.87</v>
       </c>
       <c r="M9" s="1">
-        <v>0.96241258741258739</v>
+        <v>0.89512195121951221</v>
       </c>
       <c r="N9" s="1">
-        <v>0.16339869281045752</v>
+        <v>0.36323529411764705</v>
       </c>
       <c r="O9" s="1">
         <v>0.98</v>
@@ -906,7 +905,7 @@
         <v>0.99099909990999102</v>
       </c>
       <c r="Q9" s="1">
-        <v>0.75757575757575757</v>
+        <v>0.75</v>
       </c>
       <c r="U9" s="3">
         <f>A9-L9</f>
@@ -914,11 +913,11 @@
       </c>
       <c r="V9" s="1">
         <f t="shared" ref="V9:Z9" si="4">B9-M9</f>
-        <v>3.0576019072951599E-2</v>
+        <v>-2.3774717242440735E-3</v>
       </c>
       <c r="W9" s="1">
         <f t="shared" si="4"/>
-        <v>-0.13522967872595049</v>
+        <v>-0.107421340629275</v>
       </c>
       <c r="X9" s="3">
         <f t="shared" si="4"/>
@@ -926,13 +925,13 @@
       </c>
       <c r="Y9" s="1">
         <f t="shared" si="4"/>
-        <v>-7.4921554655466016E-3</v>
+        <v>-8.3602110211021818E-3</v>
       </c>
       <c r="Z9" s="1">
         <f t="shared" si="4"/>
-        <v>-0.39393939393939392</v>
-      </c>
-      <c r="AD9" s="7">
+        <v>-0.45</v>
+      </c>
+      <c r="AD9" s="4">
         <v>0.87995955565741213</v>
       </c>
       <c r="AE9" s="1">
@@ -941,7 +940,7 @@
       <c r="AF9" s="1">
         <v>0.39229369924488566</v>
       </c>
-      <c r="AG9" s="7">
+      <c r="AG9" s="4">
         <v>0.9593259602906502</v>
       </c>
       <c r="AH9" s="1">
@@ -956,11 +955,11 @@
       </c>
       <c r="AM9" s="1">
         <f t="shared" ref="AM9:AQ9" si="5">B9-AE9</f>
-        <v>8.9279992306264044E-2</v>
+        <v>-1.096413468400681E-2</v>
       </c>
       <c r="AN9" s="1">
         <f t="shared" si="5"/>
-        <v>-0.3641246851603786</v>
+        <v>-0.13647974575651362</v>
       </c>
       <c r="AO9" s="3">
         <f t="shared" si="5"/>
@@ -968,11 +967,11 @@
       </c>
       <c r="AP9" s="1">
         <f t="shared" si="5"/>
-        <v>1.5427821438886435E-2</v>
+        <v>1.4559765883330855E-2</v>
       </c>
       <c r="AQ9" s="1">
         <f t="shared" si="5"/>
-        <v>-0.27522231916971263</v>
+        <v>-0.33885868280607628</v>
       </c>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.3">
@@ -1034,31 +1033,31 @@
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
-        <v>0.94512452511608269</v>
+        <v>0.94</v>
       </c>
       <c r="B13" s="1">
-        <v>0.99955337204108974</v>
+        <v>0.9452170248630426</v>
       </c>
       <c r="C13" s="1">
-        <v>7.6923076923076927E-3</v>
+        <v>0.13461538461538461</v>
       </c>
       <c r="D13" s="1">
         <v>0.93917785234899331</v>
       </c>
       <c r="E13" s="1">
-        <v>0.94271272114574556</v>
+        <v>0.94481887110362262</v>
       </c>
       <c r="F13" s="1">
-        <v>9.0909090909090912E-2</v>
+        <v>6.363636363636363E-2</v>
       </c>
       <c r="L13">
         <v>0.95</v>
       </c>
       <c r="M13" s="1">
-        <v>0.99396191360891784</v>
+        <v>0.95280498664292079</v>
       </c>
       <c r="N13" s="1">
-        <v>8.6206896551724144E-2</v>
+        <v>0.43478260869565216</v>
       </c>
       <c r="O13" s="1">
         <v>0.91</v>
@@ -1071,15 +1070,15 @@
       </c>
       <c r="U13" s="3">
         <f>A13-L13</f>
-        <v>-4.8754748839172635E-3</v>
+        <v>-1.0000000000000009E-2</v>
       </c>
       <c r="V13" s="1">
         <f t="shared" ref="V13:Z13" si="6">B13-M13</f>
-        <v>5.591458432171903E-3</v>
+        <v>-7.587961779878194E-3</v>
       </c>
       <c r="W13" s="1">
         <f t="shared" si="6"/>
-        <v>-7.8514588859416451E-2</v>
+        <v>-0.30016722408026753</v>
       </c>
       <c r="X13" s="3">
         <f t="shared" si="6"/>
@@ -1087,13 +1086,13 @@
       </c>
       <c r="Y13" s="1">
         <f t="shared" si="6"/>
-        <v>2.2678327336631221E-2</v>
+        <v>2.4784477294508278E-2</v>
       </c>
       <c r="Z13" s="1">
         <f t="shared" si="6"/>
-        <v>-0.25391849529780564</v>
-      </c>
-      <c r="AD13" s="7">
+        <v>-0.28119122257053297</v>
+      </c>
+      <c r="AD13" s="4">
         <v>0.93655789541389611</v>
       </c>
       <c r="AE13" s="1">
@@ -1102,7 +1101,7 @@
       <c r="AF13" s="1">
         <v>0.38817437008475791</v>
       </c>
-      <c r="AG13" s="7">
+      <c r="AG13" s="4">
         <v>0.95627927759889997</v>
       </c>
       <c r="AH13" s="1">
@@ -1113,15 +1112,15 @@
       </c>
       <c r="AL13" s="3">
         <f>A13-AD13</f>
-        <v>8.5666297021865789E-3</v>
+        <v>3.4421045861038335E-3</v>
       </c>
       <c r="AM13" s="1">
         <f t="shared" ref="AM13:AQ13" si="7">B13-AE13</f>
-        <v>5.3613490241476991E-2</v>
+        <v>-7.2285693657014871E-4</v>
       </c>
       <c r="AN13" s="1">
         <f t="shared" si="7"/>
-        <v>-0.38048206239245019</v>
+        <v>-0.25355898546937328</v>
       </c>
       <c r="AO13" s="3">
         <f t="shared" si="7"/>
@@ -1129,11 +1128,11 @@
       </c>
       <c r="AP13" s="1">
         <f t="shared" si="7"/>
-        <v>-1.9223568387618961E-2</v>
+        <v>-1.7117418429741904E-2</v>
       </c>
       <c r="AQ13" s="1">
         <f t="shared" si="7"/>
-        <v>-0.39614073665715066</v>
+        <v>-0.423413463929878</v>
       </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.3">
@@ -1160,28 +1159,28 @@
         <v>0.93962722852512159</v>
       </c>
       <c r="B15" s="1">
-        <v>0.99956877964639934</v>
+        <v>0.93856794141578515</v>
       </c>
       <c r="C15" s="1">
-        <v>6.7114093959731542E-3</v>
+        <v>0.25</v>
       </c>
       <c r="D15" s="1">
         <v>0.97273489932885904</v>
       </c>
       <c r="E15" s="1">
-        <v>0.97641112047177758</v>
+        <v>0.97177759056444823</v>
       </c>
       <c r="F15" s="1">
-        <v>9.0909090909090912E-2</v>
+        <v>0.20909090909090908</v>
       </c>
       <c r="L15">
         <v>0.93</v>
       </c>
       <c r="M15" s="1">
-        <v>0.98080204778156999</v>
+        <v>0.94259942599425994</v>
       </c>
       <c r="N15" s="1">
-        <v>0.13043478260869565</v>
+        <v>0.31818181818181818</v>
       </c>
       <c r="O15" s="1">
         <v>0.99</v>
@@ -1198,11 +1197,11 @@
       </c>
       <c r="V15" s="1">
         <f t="shared" ref="V15:Z15" si="8">B15-M15</f>
-        <v>1.8766731864829356E-2</v>
+        <v>-4.0314845784747977E-3</v>
       </c>
       <c r="W15" s="1">
         <f t="shared" si="8"/>
-        <v>-0.12372337321272249</v>
+        <v>-6.8181818181818177E-2</v>
       </c>
       <c r="X15" s="3">
         <f t="shared" si="8"/>
@@ -1210,13 +1209,13 @@
       </c>
       <c r="Y15" s="1">
         <f t="shared" si="8"/>
-        <v>-1.1980968952126081E-2</v>
+        <v>-1.6614498859455429E-2</v>
       </c>
       <c r="Z15" s="1">
         <f t="shared" si="8"/>
-        <v>-0.63322884012539182</v>
-      </c>
-      <c r="AD15" s="7">
+        <v>-0.51504702194357366</v>
+      </c>
+      <c r="AD15" s="4">
         <v>0.93150652982465443</v>
       </c>
       <c r="AE15" s="1">
@@ -1225,7 +1224,7 @@
       <c r="AF15" s="1">
         <v>0.37053375707013869</v>
       </c>
-      <c r="AG15" s="7">
+      <c r="AG15" s="4">
         <v>0.97090784893787263</v>
       </c>
       <c r="AH15" s="1">
@@ -1240,11 +1239,11 @@
       </c>
       <c r="AM15" s="1">
         <f t="shared" ref="AM15:AQ15" si="9">B15-AE15</f>
-        <v>5.5868047085929073E-2</v>
+        <v>-5.1327911446851227E-3</v>
       </c>
       <c r="AN15" s="1">
         <f t="shared" si="9"/>
-        <v>-0.36382234767416555</v>
+        <v>-0.12053375707013869</v>
       </c>
       <c r="AO15" s="3">
         <f t="shared" si="9"/>
@@ -1252,11 +1251,11 @@
       </c>
       <c r="AP15" s="1">
         <f t="shared" si="9"/>
-        <v>1.0105561730051615E-3</v>
+        <v>-3.6229737343241863E-3</v>
       </c>
       <c r="AQ15" s="1">
         <f t="shared" si="9"/>
-        <v>-0.50890955098823387</v>
+        <v>-0.39072773280641571</v>
       </c>
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.3">
@@ -1283,28 +1282,28 @@
         <v>0.94989106753812635</v>
       </c>
       <c r="B17" s="1">
-        <v>1</v>
+        <v>0.94952132288946911</v>
       </c>
       <c r="C17" s="1">
-        <v>0</v>
+        <v>0.14705882352941177</v>
       </c>
       <c r="D17" s="1">
-        <v>0.91442953020134232</v>
+        <v>0.92</v>
       </c>
       <c r="E17" s="1">
-        <v>0.91828138163437234</v>
+        <v>0.91912384161752314</v>
       </c>
       <c r="F17" s="1">
-        <v>0</v>
+        <v>4.5454545454545456E-2</v>
       </c>
       <c r="L17">
         <v>0.94</v>
       </c>
       <c r="M17" s="1">
-        <v>0.99178457325422187</v>
+        <v>0.95140105078809112</v>
       </c>
       <c r="N17" s="1">
-        <v>9.0163934426229511E-2</v>
+        <v>0.37931034482758619</v>
       </c>
       <c r="O17" s="1">
         <v>0.93</v>
@@ -1321,25 +1320,25 @@
       </c>
       <c r="V17" s="1">
         <f t="shared" ref="V17:Z17" si="10">B17-M17</f>
-        <v>8.2154267457781316E-3</v>
+        <v>-1.8797278986220078E-3</v>
       </c>
       <c r="W17" s="1">
         <f t="shared" si="10"/>
-        <v>-9.0163934426229511E-2</v>
+        <v>-0.23225152129817442</v>
       </c>
       <c r="X17" s="3">
         <f t="shared" si="10"/>
-        <v>-1.5570469798657727E-2</v>
+        <v>-1.0000000000000009E-2</v>
       </c>
       <c r="Y17" s="1">
         <f t="shared" si="10"/>
-        <v>-1.5940458434415272E-2</v>
+        <v>-1.5097998451264472E-2</v>
       </c>
       <c r="Z17" s="1">
         <f t="shared" si="10"/>
-        <v>-0.37931034482758619</v>
-      </c>
-      <c r="AD17" s="7">
+        <v>-0.33385579937304072</v>
+      </c>
+      <c r="AD17" s="4">
         <v>0.92835083465222401</v>
       </c>
       <c r="AE17" s="1">
@@ -1348,7 +1347,7 @@
       <c r="AF17" s="1">
         <v>0.3620199063806267</v>
       </c>
-      <c r="AG17" s="7">
+      <c r="AG17" s="4">
         <v>0.97845790673565081</v>
       </c>
       <c r="AH17" s="1">
@@ -1363,23 +1362,23 @@
       </c>
       <c r="AM17" s="1">
         <f t="shared" ref="AM17:AQ17" si="11">B17-AE17</f>
-        <v>5.7648922063396113E-2</v>
+        <v>7.1702449528652235E-3</v>
       </c>
       <c r="AN17" s="1">
         <f t="shared" si="11"/>
-        <v>-0.3620199063806267</v>
+        <v>-0.21496108285121493</v>
       </c>
       <c r="AO17" s="3">
         <f t="shared" si="11"/>
-        <v>-6.4028376534308484E-2</v>
+        <v>-5.8457906735650766E-2</v>
       </c>
       <c r="AP17" s="1">
         <f t="shared" si="11"/>
-        <v>-6.3806462259855645E-2</v>
+        <v>-6.2964002276704845E-2</v>
       </c>
       <c r="AQ17" s="1">
         <f t="shared" si="11"/>
-        <v>-0.67982831522213616</v>
+        <v>-0.63437376976759074</v>
       </c>
     </row>
   </sheetData>
@@ -1406,38 +1405,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="L1" s="4" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="L1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="U1" s="5" t="s">
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="U1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="V1" s="5"/>
-      <c r="W1" s="5"/>
-      <c r="X1" s="5"/>
-      <c r="Y1" s="5"/>
-      <c r="Z1" s="5"/>
-      <c r="AD1" s="4" t="s">
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="9"/>
+      <c r="Z1" s="9"/>
+      <c r="AD1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="AE1" s="4"/>
-      <c r="AF1" s="4"/>
-      <c r="AG1" s="4"/>
-      <c r="AH1" s="4"/>
-      <c r="AI1" s="4"/>
+      <c r="AE1" s="8"/>
+      <c r="AF1" s="8"/>
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="8"/>
+      <c r="AI1" s="8"/>
       <c r="AL1" s="2" t="s">
         <v>10</v>
       </c>
@@ -1536,31 +1535,31 @@
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
-        <v>0.92928176795580109</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
+        <v>0.93</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0.93</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5" s="1">
-        <v>0.72003424657534243</v>
+        <v>0.72</v>
       </c>
       <c r="E5" s="1">
-        <v>0.72003424657534243</v>
+        <v>0.72</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="M5" s="1">
-        <v>0.7847025495750708</v>
+        <v>0.98576512455516019</v>
       </c>
       <c r="N5" s="1">
-        <v>0.87096774193548387</v>
+        <v>0.26213592233009708</v>
       </c>
       <c r="O5" s="1">
         <v>0.38996138996138996</v>
@@ -1573,23 +1572,23 @@
       </c>
       <c r="U5" s="3">
         <f>A5-L5</f>
-        <v>0.15928176795580107</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="V5" s="1">
         <f t="shared" ref="V5:Z5" si="0">B5-M5</f>
-        <v>0.2152974504249292</v>
+        <v>-5.5765124555160139E-2</v>
       </c>
       <c r="W5" s="1">
         <f t="shared" si="0"/>
-        <v>-0.87096774193548387</v>
+        <v>-0.26213592233009708</v>
       </c>
       <c r="X5" s="3">
         <f>D5-O5</f>
-        <v>0.33007285661395247</v>
+        <v>0.33003861003861001</v>
       </c>
       <c r="Y5" s="1">
         <f t="shared" si="0"/>
-        <v>0.28654441871931741</v>
+        <v>0.28651017214397495</v>
       </c>
       <c r="Z5" s="1">
         <f t="shared" si="0"/>
@@ -1615,11 +1614,11 @@
       </c>
       <c r="AL5" s="3">
         <f>A5-AD5</f>
-        <v>0.92928176795580109</v>
+        <v>0.93</v>
       </c>
       <c r="AM5" s="1">
         <f t="shared" ref="AM5:AQ5" si="1">B5-AE5</f>
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AN5" s="1">
         <f t="shared" si="1"/>
@@ -1627,11 +1626,11 @@
       </c>
       <c r="AO5" s="3">
         <f t="shared" si="1"/>
-        <v>0.72003424657534243</v>
+        <v>0.72</v>
       </c>
       <c r="AP5" s="1">
         <f t="shared" si="1"/>
-        <v>0.72003424657534243</v>
+        <v>0.72</v>
       </c>
       <c r="AQ5" s="1">
         <f t="shared" si="1"/>
@@ -1656,31 +1655,31 @@
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
-        <v>0.88952536824877249</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
+        <v>0.89</v>
+      </c>
+      <c r="B7" s="1">
+        <v>0.89</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7" s="1">
-        <v>0.93065068493150682</v>
+        <v>0.93</v>
       </c>
       <c r="E7" s="1">
-        <v>0.93065068493150682</v>
+        <v>0.93</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="M7" s="1">
-        <v>0.75539568345323738</v>
+        <v>0.98130841121495327</v>
       </c>
       <c r="N7" s="1">
-        <v>0.86440677966101698</v>
+        <v>0.27272727272727271</v>
       </c>
       <c r="O7" s="1">
         <v>0.60617760617760619</v>
@@ -1693,23 +1692,23 @@
       </c>
       <c r="U7" s="3">
         <f>A7-L7</f>
-        <v>0.12952536824877248</v>
+        <v>0.12</v>
       </c>
       <c r="V7" s="1">
         <f t="shared" ref="V7:Z7" si="2">B7-M7</f>
-        <v>0.24460431654676262</v>
+        <v>-9.1308411214953256E-2</v>
       </c>
       <c r="W7" s="1">
         <f t="shared" si="2"/>
-        <v>-0.86440677966101698</v>
+        <v>-0.27272727272727271</v>
       </c>
       <c r="X7" s="3">
         <f>D7-O7</f>
-        <v>0.32447307875390063</v>
+        <v>0.32382239382239386</v>
       </c>
       <c r="Y7" s="1">
         <f t="shared" si="2"/>
-        <v>0.27337368962634245</v>
+        <v>0.27272300469483568</v>
       </c>
       <c r="Z7" s="1">
         <f t="shared" si="2"/>
@@ -1735,11 +1734,11 @@
       </c>
       <c r="AL7" s="3">
         <f>A7-AD7</f>
-        <v>0.88952536824877249</v>
+        <v>0.89</v>
       </c>
       <c r="AM7" s="1">
         <f t="shared" ref="AM7:AQ7" si="3">B7-AE7</f>
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AN7" s="1">
         <f t="shared" si="3"/>
@@ -1747,11 +1746,11 @@
       </c>
       <c r="AO7" s="3">
         <f t="shared" si="3"/>
-        <v>0.93065068493150682</v>
+        <v>0.93</v>
       </c>
       <c r="AP7" s="1">
         <f t="shared" si="3"/>
-        <v>0.93065068493150682</v>
+        <v>0.93</v>
       </c>
       <c r="AQ7" s="1">
         <f t="shared" si="3"/>
@@ -1776,19 +1775,19 @@
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
-        <v>0.88452474469756481</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
+        <v>0.88</v>
+      </c>
+      <c r="B9" s="1">
+        <v>0.88</v>
       </c>
       <c r="C9">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D9" s="1">
-        <v>0.96404109589041098</v>
+        <v>0.97</v>
       </c>
       <c r="E9" s="1">
-        <v>0.96404109589041098</v>
+        <v>0.97</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1797,45 +1796,45 @@
         <v>0.7</v>
       </c>
       <c r="M9" s="1">
-        <v>0.67488443759630201</v>
+        <v>0.98206278026905824</v>
       </c>
       <c r="N9" s="1">
-        <v>0.90123456790123457</v>
+        <v>0.25704225352112675</v>
       </c>
       <c r="O9" s="1">
         <v>0.65765765765765771</v>
       </c>
       <c r="P9" s="1">
-        <v>0.68544600938967137</v>
+        <v>0.69</v>
       </c>
       <c r="Q9" s="1">
         <v>0.52898550724637683</v>
       </c>
       <c r="U9" s="3">
         <f>A9-L9</f>
-        <v>0.18452474469756486</v>
+        <v>0.18000000000000005</v>
       </c>
       <c r="V9" s="1">
         <f t="shared" ref="V9:Z9" si="4">B9-M9</f>
-        <v>0.32511556240369799</v>
+        <v>-0.10206278026905824</v>
       </c>
       <c r="W9" s="1">
         <f t="shared" si="4"/>
-        <v>-0.89123456790123456</v>
+        <v>-0.25704225352112675</v>
       </c>
       <c r="X9" s="3">
         <f>D9-O9</f>
-        <v>0.30638343823275327</v>
+        <v>0.31234234234234226</v>
       </c>
       <c r="Y9" s="1">
-        <f t="shared" si="4"/>
-        <v>0.27859508650073961</v>
+        <f>E9-P9</f>
+        <v>0.28000000000000003</v>
       </c>
       <c r="Z9" s="1">
         <f t="shared" si="4"/>
         <v>-0.52898550724637683</v>
       </c>
-      <c r="AD9" s="7">
+      <c r="AD9" s="4">
         <v>0.67219648110612795</v>
       </c>
       <c r="AE9" s="1">
@@ -1844,7 +1843,7 @@
       <c r="AF9" s="1">
         <v>0.25876068380073264</v>
       </c>
-      <c r="AG9" s="7">
+      <c r="AG9" s="4">
         <v>3.7777172854017799E-2</v>
       </c>
       <c r="AH9" s="1">
@@ -1855,23 +1854,23 @@
       </c>
       <c r="AL9" s="3">
         <f>A9-AD9</f>
-        <v>0.21232826359143686</v>
+        <v>0.20780351889387205</v>
       </c>
       <c r="AM9" s="1">
         <f t="shared" ref="AM9:AQ9" si="5">B9-AE9</f>
-        <v>8.0759981037037409E-3</v>
+        <v>-0.11192400189629625</v>
       </c>
       <c r="AN9" s="1">
         <f t="shared" si="5"/>
-        <v>-0.24876068380073263</v>
+        <v>-0.25876068380073264</v>
       </c>
       <c r="AO9" s="3">
         <f t="shared" si="5"/>
-        <v>0.92626392303639316</v>
+        <v>0.93222282714598215</v>
       </c>
       <c r="AP9" s="1">
         <f t="shared" si="5"/>
-        <v>0.92451666563297297</v>
+        <v>0.93047556974256196</v>
       </c>
       <c r="AQ9" s="1">
         <f t="shared" si="5"/>
@@ -1928,31 +1927,31 @@
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
-        <v>0.94134775374376045</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
+        <v>0.94</v>
+      </c>
+      <c r="B13" s="1">
+        <v>0.94</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13" s="1">
-        <v>0.94844928751047775</v>
+        <v>0.95</v>
       </c>
       <c r="E13" s="1">
-        <v>0.95044099118017644</v>
+        <v>0.95</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="M13" s="1">
-        <v>0.81308411214953269</v>
+        <v>0.98676748582230622</v>
       </c>
       <c r="N13" s="1">
-        <v>0.87755102040816324</v>
+        <v>0.26134969325153373</v>
       </c>
       <c r="O13" s="1">
         <v>0.31</v>
@@ -1961,33 +1960,33 @@
         <v>0.30225825130283729</v>
       </c>
       <c r="Q13" s="1">
-        <v>0.34677419354838712</v>
+        <v>0.34</v>
       </c>
       <c r="U13" s="3">
         <f>A13-L13</f>
-        <v>0.1313477537437604</v>
+        <v>0.12</v>
       </c>
       <c r="V13" s="1">
         <f t="shared" ref="V13:Z13" si="6">B13-M13</f>
-        <v>0.18691588785046731</v>
+        <v>-4.6767485822306276E-2</v>
       </c>
       <c r="W13" s="1">
         <f t="shared" si="6"/>
-        <v>-0.87755102040816324</v>
+        <v>-0.26134969325153373</v>
       </c>
       <c r="X13" s="3">
         <f>D13-O13</f>
-        <v>0.63844928751047769</v>
+        <v>0.6399999999999999</v>
       </c>
       <c r="Y13" s="1">
         <f t="shared" si="6"/>
-        <v>0.64818273987733921</v>
+        <v>0.64774174869716261</v>
       </c>
       <c r="Z13" s="1">
         <f t="shared" si="6"/>
-        <v>-0.34677419354838712</v>
-      </c>
-      <c r="AD13" s="7">
+        <v>-0.34</v>
+      </c>
+      <c r="AD13" s="4">
         <v>0.2</v>
       </c>
       <c r="AE13" s="1">
@@ -1996,7 +1995,7 @@
       <c r="AF13" s="1">
         <v>0.2</v>
       </c>
-      <c r="AG13" s="7">
+      <c r="AG13" s="4">
         <v>1.5938580000000001E-4</v>
       </c>
       <c r="AH13" s="1">
@@ -2007,11 +2006,11 @@
       </c>
       <c r="AL13" s="3">
         <f>A13-AD13</f>
-        <v>0.7413477537437605</v>
+        <v>0.74</v>
       </c>
       <c r="AM13" s="1">
         <f t="shared" ref="AM13:AQ13" si="7">B13-AE13</f>
-        <v>1</v>
+        <v>0.94</v>
       </c>
       <c r="AN13" s="1">
         <f t="shared" si="7"/>
@@ -2019,11 +2018,11 @@
       </c>
       <c r="AO13" s="3">
         <f t="shared" si="7"/>
-        <v>0.94828990171047778</v>
+        <v>0.94984061419999999</v>
       </c>
       <c r="AP13" s="1">
         <f t="shared" si="7"/>
-        <v>0.95044099118017644</v>
+        <v>0.95</v>
       </c>
       <c r="AQ13" s="1">
         <f t="shared" si="7"/>
@@ -2032,6 +2031,7 @@
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="M14" s="1"/>
@@ -2048,31 +2048,31 @@
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
-        <v>0.93724696356275305</v>
-      </c>
-      <c r="B15">
-        <v>1</v>
+        <v>0.94</v>
+      </c>
+      <c r="B15" s="1">
+        <v>0.94</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15" s="1">
-        <v>0.97024308466051967</v>
+        <v>0.97</v>
       </c>
       <c r="E15" s="1">
-        <v>0.97228055438891225</v>
+        <v>0.97</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0.8</v>
+        <v>0.81</v>
       </c>
       <c r="M15" s="1">
-        <v>0.80815347721822539</v>
+        <v>0.98060135790494662</v>
       </c>
       <c r="N15" s="1">
-        <v>0.77419354838709675</v>
+        <v>0.23076923076923078</v>
       </c>
       <c r="O15" s="1">
         <v>0.59</v>
@@ -2085,29 +2085,29 @@
       </c>
       <c r="U15" s="3">
         <f>A15-L15</f>
-        <v>0.13724696356275301</v>
+        <v>0.12999999999999989</v>
       </c>
       <c r="V15" s="1">
         <f t="shared" ref="V15:Z15" si="8">B15-M15</f>
-        <v>0.19184652278177461</v>
+        <v>-4.0601357904946678E-2</v>
       </c>
       <c r="W15" s="1">
         <f t="shared" si="8"/>
-        <v>-0.77419354838709675</v>
+        <v>-0.23076923076923078</v>
       </c>
       <c r="X15" s="3">
         <f>D15-O15</f>
-        <v>0.3802430846605197</v>
+        <v>0.38</v>
       </c>
       <c r="Y15" s="1">
         <f t="shared" si="8"/>
-        <v>0.38687233203801474</v>
+        <v>0.38459177764910246</v>
       </c>
       <c r="Z15" s="1">
         <f t="shared" si="8"/>
         <v>-0.58064516129032262</v>
       </c>
-      <c r="AD15" s="7">
+      <c r="AD15" s="4">
         <v>0.61559422054545454</v>
       </c>
       <c r="AE15" s="1">
@@ -2116,7 +2116,7 @@
       <c r="AF15" s="1">
         <v>0.30664508818181824</v>
       </c>
-      <c r="AG15" s="7">
+      <c r="AG15" s="4">
         <v>3.2510241000000002E-2</v>
       </c>
       <c r="AH15" s="1">
@@ -2127,11 +2127,11 @@
       </c>
       <c r="AL15" s="3">
         <f>A15-AD15</f>
-        <v>0.32165274301729851</v>
+        <v>0.32440577945454541</v>
       </c>
       <c r="AM15" s="1">
         <f t="shared" ref="AM15:AQ15" si="9">B15-AE15</f>
-        <v>0</v>
+        <v>-6.0000000000000053E-2</v>
       </c>
       <c r="AN15" s="1">
         <f t="shared" si="9"/>
@@ -2139,11 +2139,11 @@
       </c>
       <c r="AO15" s="3">
         <f t="shared" si="9"/>
-        <v>0.93773284366051968</v>
+        <v>0.93748975899999998</v>
       </c>
       <c r="AP15" s="1">
         <f t="shared" si="9"/>
-        <v>0.94665001084345768</v>
+        <v>0.9443694564545454</v>
       </c>
       <c r="AQ15" s="1">
         <f t="shared" si="9"/>
@@ -2152,6 +2152,7 @@
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="M16" s="1"/>
@@ -2168,19 +2169,19 @@
     </row>
     <row r="17" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <v>0.94684528954191871</v>
-      </c>
-      <c r="B17">
-        <v>1</v>
+        <v>0.95</v>
+      </c>
+      <c r="B17" s="1">
+        <v>0.95</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17" s="1">
-        <v>0.91827326068734283</v>
+        <v>0.92</v>
       </c>
       <c r="E17" s="1">
-        <v>0.9202015959680806</v>
+        <v>0.92</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -2189,10 +2190,10 @@
         <v>0.78</v>
       </c>
       <c r="M17" s="1">
-        <v>0.78115682766845562</v>
+        <v>0.97253155159613958</v>
       </c>
       <c r="N17" s="1">
-        <v>0.72180451127819545</v>
+        <v>0.20734341252699784</v>
       </c>
       <c r="O17" s="1">
         <v>0.76</v>
@@ -2205,29 +2206,29 @@
       </c>
       <c r="U17" s="3">
         <f>A17-L17</f>
-        <v>0.16684528954191868</v>
+        <v>0.16999999999999993</v>
       </c>
       <c r="V17" s="1">
         <f t="shared" ref="V17:Z17" si="10">B17-M17</f>
-        <v>0.21884317233154438</v>
+        <v>-2.2531551596139621E-2</v>
       </c>
       <c r="W17" s="1">
         <f t="shared" si="10"/>
-        <v>-0.72180451127819545</v>
+        <v>-0.20734341252699784</v>
       </c>
       <c r="X17" s="3">
         <f>D17-O17</f>
-        <v>0.15827326068734282</v>
+        <v>0.16000000000000003</v>
       </c>
       <c r="Y17" s="1">
         <f t="shared" si="10"/>
-        <v>0.16166077373299081</v>
+        <v>0.16145917776491026</v>
       </c>
       <c r="Z17" s="1">
         <f t="shared" si="10"/>
         <v>-0.77419354838709675</v>
       </c>
-      <c r="AD17" s="7">
+      <c r="AD17" s="4">
         <v>0.75477757894000008</v>
       </c>
       <c r="AE17" s="1">
@@ -2236,7 +2237,7 @@
       <c r="AF17" s="1">
         <v>0.28000000000000003</v>
       </c>
-      <c r="AG17" s="7">
+      <c r="AG17" s="4">
         <v>0.14306746273999998</v>
       </c>
       <c r="AH17" s="1">
@@ -2247,11 +2248,11 @@
       </c>
       <c r="AL17" s="3">
         <f>A17-AD17</f>
-        <v>0.19206771060191863</v>
+        <v>0.19522242105999987</v>
       </c>
       <c r="AM17" s="1">
         <f t="shared" ref="AM17:AQ17" si="11">B17-AE17</f>
-        <v>5.7534739600002549E-3</v>
+        <v>-4.424652603999979E-2</v>
       </c>
       <c r="AN17" s="1">
         <f t="shared" si="11"/>
@@ -2259,11 +2260,11 @@
       </c>
       <c r="AO17" s="3">
         <f t="shared" si="11"/>
-        <v>0.77520579794734279</v>
+        <v>0.77693253726</v>
       </c>
       <c r="AP17" s="1">
         <f t="shared" si="11"/>
-        <v>0.79020159596808059</v>
+        <v>0.79</v>
       </c>
       <c r="AQ17" s="1">
         <f t="shared" si="11"/>
@@ -2293,47 +2294,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="L1" s="4" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="L1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="U1" s="5" t="s">
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="U1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="V1" s="5"/>
-      <c r="W1" s="5"/>
-      <c r="X1" s="5"/>
-      <c r="Y1" s="5"/>
-      <c r="Z1" s="5"/>
-      <c r="AA1" s="6"/>
-      <c r="AD1" s="4" t="s">
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="9"/>
+      <c r="Z1" s="9"/>
+      <c r="AD1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="AE1" s="4"/>
-      <c r="AF1" s="4"/>
-      <c r="AG1" s="4"/>
-      <c r="AH1" s="4"/>
-      <c r="AI1" s="4"/>
-      <c r="AL1" s="5" t="s">
+      <c r="AE1" s="8"/>
+      <c r="AF1" s="8"/>
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="8"/>
+      <c r="AI1" s="8"/>
+      <c r="AL1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="AM1" s="5"/>
-      <c r="AN1" s="5"/>
-      <c r="AO1" s="5"/>
-      <c r="AP1" s="5"/>
-      <c r="AQ1" s="5"/>
+      <c r="AM1" s="9"/>
+      <c r="AN1" s="9"/>
+      <c r="AO1" s="9"/>
+      <c r="AP1" s="9"/>
+      <c r="AQ1" s="9"/>
     </row>
     <row r="2" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -2432,10 +2432,10 @@
         <v>0.91072400653238972</v>
       </c>
       <c r="B5" s="1">
-        <v>0.99273167777104787</v>
+        <v>0.9151785714285714</v>
       </c>
       <c r="C5" s="1">
-        <v>0.18279569892473119</v>
+        <v>0.75555555555555554</v>
       </c>
       <c r="D5" s="1">
         <v>0.45203998919211025</v>
@@ -2450,10 +2450,10 @@
         <v>0.91</v>
       </c>
       <c r="M5" s="1">
-        <v>0.99508901166359731</v>
+        <v>0.91530208921513267</v>
       </c>
       <c r="N5" s="1">
-        <v>0.18032786885245902</v>
+        <v>0.80487804878048785</v>
       </c>
       <c r="O5" s="1">
         <v>0.45</v>
@@ -2469,12 +2469,12 @@
         <v>7.2400653238968715E-4</v>
       </c>
       <c r="V5" s="1">
-        <f t="shared" ref="V5:Z5" si="0">B5-M5</f>
-        <v>-2.3573338925494403E-3</v>
+        <f>B5-M5</f>
+        <v>-1.2351778656127799E-4</v>
       </c>
       <c r="W5" s="1">
-        <f t="shared" si="0"/>
-        <v>2.4678300722721647E-3</v>
+        <f t="shared" ref="W5:Z5" si="0">C5-N5</f>
+        <v>-4.9322493224932318E-2</v>
       </c>
       <c r="X5" s="3">
         <f t="shared" si="0"/>
@@ -2488,7 +2488,7 @@
         <f t="shared" si="0"/>
         <v>8.4097280096976923E-3</v>
       </c>
-      <c r="AD5" s="10">
+      <c r="AD5" s="7">
         <v>0.94594594594594583</v>
       </c>
       <c r="AE5" s="1">
@@ -2497,7 +2497,7 @@
       <c r="AF5" s="1">
         <v>0.81818181818181823</v>
       </c>
-      <c r="AG5" s="10">
+      <c r="AG5" s="7">
         <v>4.720798489344484E-2</v>
       </c>
       <c r="AH5" s="1">
@@ -2512,11 +2512,11 @@
       </c>
       <c r="AM5" s="1">
         <f t="shared" ref="AM5:AQ5" si="1">B5-AE5</f>
-        <v>3.8708689265300911E-2</v>
+        <v>-3.8844417077175564E-2</v>
       </c>
       <c r="AN5" s="1">
         <f t="shared" si="1"/>
-        <v>-0.6353861192570871</v>
+        <v>-6.2626262626262696E-2</v>
       </c>
       <c r="AO5" s="3">
         <f t="shared" si="1"/>
@@ -2549,10 +2549,10 @@
         <v>0.89054545454545453</v>
       </c>
       <c r="B7" s="1">
-        <v>0.99047619047619051</v>
+        <v>0.89588014981273412</v>
       </c>
       <c r="C7" s="1">
-        <v>0.17014925373134329</v>
+        <v>0.71698113207547165</v>
       </c>
       <c r="D7" s="1">
         <v>0.66171305052688467</v>
@@ -2567,10 +2567,10 @@
         <v>0.89</v>
       </c>
       <c r="M7" s="1">
-        <v>0.99097250718096019</v>
+        <v>0.89510748702742771</v>
       </c>
       <c r="N7" s="1">
-        <v>0.15522388059701492</v>
+        <v>0.70270270270270274</v>
       </c>
       <c r="O7" s="1">
         <v>0.67</v>
@@ -2587,11 +2587,11 @@
       </c>
       <c r="V7" s="1">
         <f t="shared" ref="V7:Z7" si="2">B7-M7</f>
-        <v>-4.963167047696837E-4</v>
+        <v>7.7266278530641053E-4</v>
       </c>
       <c r="W7" s="1">
         <f t="shared" si="2"/>
-        <v>1.4925373134328374E-2</v>
+        <v>1.4278429372768908E-2</v>
       </c>
       <c r="X7" s="3">
         <f t="shared" si="2"/>
@@ -2605,7 +2605,7 @@
         <f t="shared" si="2"/>
         <v>3.0633633861151088E-2</v>
       </c>
-      <c r="AD7" s="10">
+      <c r="AD7" s="7">
         <v>0.92405063291139222</v>
       </c>
       <c r="AE7" s="1">
@@ -2614,7 +2614,7 @@
       <c r="AF7" s="1">
         <v>0.75</v>
       </c>
-      <c r="AG7" s="10">
+      <c r="AG7" s="7">
         <v>0.11815484219045048</v>
       </c>
       <c r="AH7" s="1">
@@ -2629,11 +2629,11 @@
       </c>
       <c r="AM7" s="1">
         <f t="shared" ref="AM7:AQ7" si="3">B7-AE7</f>
-        <v>6.0345186109378335E-2</v>
+        <v>-3.4250854554078058E-2</v>
       </c>
       <c r="AN7" s="1">
         <f t="shared" si="3"/>
-        <v>-0.57985074626865674</v>
+        <v>-3.301886792452835E-2</v>
       </c>
       <c r="AO7" s="3">
         <f t="shared" si="3"/>
@@ -2666,10 +2666,10 @@
         <v>0.86423274386765547</v>
       </c>
       <c r="B9" s="1">
-        <v>0.9849447975911676</v>
+        <v>0.87229629629629635</v>
       </c>
       <c r="C9" s="1">
-        <v>0.16634429400386846</v>
+        <v>0.65648854961832059</v>
       </c>
       <c r="D9" s="1">
         <v>0.81869764928397726</v>
@@ -2684,10 +2684,10 @@
         <v>0.86</v>
       </c>
       <c r="M9" s="1">
-        <v>0.98567144285238251</v>
+        <v>0.87179487179487181</v>
       </c>
       <c r="N9" s="1">
-        <v>0.17457305502846299</v>
+        <v>0.67647058823529416</v>
       </c>
       <c r="O9" s="1">
         <v>0.82</v>
@@ -2704,11 +2704,11 @@
       </c>
       <c r="V9" s="1">
         <f t="shared" ref="V9:Z9" si="4">B9-M9</f>
-        <v>-7.266452612149088E-4</v>
+        <v>5.0142450142454109E-4</v>
       </c>
       <c r="W9" s="1">
         <f t="shared" si="4"/>
-        <v>-8.228761024594522E-3</v>
+        <v>-1.9982038616973563E-2</v>
       </c>
       <c r="X9" s="3">
         <f t="shared" si="4"/>
@@ -2722,7 +2722,7 @@
         <f t="shared" si="4"/>
         <v>-2.1163219435815894E-2</v>
       </c>
-      <c r="AD9" s="10">
+      <c r="AD9" s="7">
         <v>0.93081081081081074</v>
       </c>
       <c r="AE9" s="1">
@@ -2731,7 +2731,7 @@
       <c r="AF9" s="1">
         <v>0.79999999999999993</v>
       </c>
-      <c r="AG9" s="10">
+      <c r="AG9" s="7">
         <v>0.23226328567574855</v>
       </c>
       <c r="AH9" s="1">
@@ -2746,11 +2746,11 @@
       </c>
       <c r="AM9" s="1">
         <f t="shared" ref="AM9:AQ9" si="5">B9-AE9</f>
-        <v>5.0500353146722965E-2</v>
+        <v>-6.2148148148148286E-2</v>
       </c>
       <c r="AN9" s="1">
         <f t="shared" si="5"/>
-        <v>-0.63365570599613141</v>
+        <v>-0.14351145038167934</v>
       </c>
       <c r="AO9" s="3">
         <f t="shared" si="5"/>
@@ -2809,10 +2809,10 @@
         <v>0.90832696715049654</v>
       </c>
       <c r="B13" s="1">
-        <v>0.99873896595208067</v>
+        <v>0.90829193733282387</v>
       </c>
       <c r="C13" s="1">
-        <v>8.368200836820083E-3</v>
+        <v>0.18</v>
       </c>
       <c r="D13" s="1">
         <v>0.58156028368794321</v>
@@ -2821,16 +2821,16 @@
         <v>0.58421440865502827</v>
       </c>
       <c r="F13" s="1">
-        <v>8.6956521739130432E-2</v>
+        <v>4.3478260869565216E-2</v>
       </c>
       <c r="L13">
         <v>0.91</v>
       </c>
       <c r="M13" s="1">
-        <v>0.999185667752443</v>
+        <v>0.90788013318534966</v>
       </c>
       <c r="N13" s="1">
-        <v>4.0000000000000001E-3</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="O13" s="1">
         <v>0.6</v>
@@ -2847,11 +2847,11 @@
       </c>
       <c r="V13" s="1">
         <f t="shared" ref="V13:Z13" si="6">B13-M13</f>
-        <v>-4.4670180036232576E-4</v>
+        <v>4.1180414747421512E-4</v>
       </c>
       <c r="W13" s="1">
         <f t="shared" si="6"/>
-        <v>4.3682008368200829E-3</v>
+        <v>-0.15333333333333332</v>
       </c>
       <c r="X13" s="3">
         <f t="shared" si="6"/>
@@ -2863,9 +2863,9 @@
       </c>
       <c r="Z13" s="1">
         <f t="shared" si="6"/>
-        <v>4.6956521739130432E-2</v>
-      </c>
-      <c r="AD13" s="10">
+        <v>3.4782608695652154E-3</v>
+      </c>
+      <c r="AD13" s="7">
         <v>0.90196078431372562</v>
       </c>
       <c r="AE13" s="1">
@@ -2874,7 +2874,7 @@
       <c r="AF13" s="1">
         <v>0</v>
       </c>
-      <c r="AG13" s="10">
+      <c r="AG13" s="7">
         <v>1.1352517345668032E-2</v>
       </c>
       <c r="AH13" s="1">
@@ -2889,11 +2889,11 @@
       </c>
       <c r="AM13" s="1">
         <f t="shared" ref="AM13:AQ13" si="7">B13-AE13</f>
-        <v>7.873896595208052E-2</v>
+        <v>-1.1708062667176278E-2</v>
       </c>
       <c r="AN13" s="1">
         <f t="shared" si="7"/>
-        <v>8.368200836820083E-3</v>
+        <v>0.18</v>
       </c>
       <c r="AO13" s="3">
         <f t="shared" si="7"/>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="AQ13" s="1">
         <f t="shared" si="7"/>
-        <v>8.6956521739130432E-2</v>
+        <v>4.3478260869565216E-2</v>
       </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.3">
@@ -2926,28 +2926,28 @@
         <v>0.87935323383084574</v>
       </c>
       <c r="B15" s="1">
-        <v>0.99858557284299854</v>
+        <v>0.8800797806033408</v>
       </c>
       <c r="C15" s="1">
-        <v>1.0309278350515464E-2</v>
+        <v>0.38750000000000001</v>
       </c>
       <c r="D15" s="1">
-        <v>0.86451455123502075</v>
+        <v>0.87</v>
       </c>
       <c r="E15" s="1">
-        <v>0.86796164248832064</v>
+        <v>0.87</v>
       </c>
       <c r="F15" s="1">
-        <v>0.21739130434782608</v>
+        <v>0.13478260869565217</v>
       </c>
       <c r="L15">
         <v>0.88</v>
       </c>
       <c r="M15" s="1">
-        <v>0.99859471613265882</v>
+        <v>0.8796731864322852</v>
       </c>
       <c r="N15" s="1">
-        <v>1.0183299389002037E-2</v>
+        <v>0.5</v>
       </c>
       <c r="O15" s="1">
         <v>0.87</v>
@@ -2964,25 +2964,25 @@
       </c>
       <c r="V15" s="1">
         <f t="shared" ref="V15:Z15" si="8">B15-M15</f>
-        <v>-9.1432896602849922E-6</v>
+        <v>4.0659417105559648E-4</v>
       </c>
       <c r="W15" s="1">
         <f t="shared" si="8"/>
-        <v>1.2597896151342672E-4</v>
+        <v>-0.11249999999999999</v>
       </c>
       <c r="X15" s="3">
         <f t="shared" si="8"/>
-        <v>-5.4854487649792505E-3</v>
+        <v>0</v>
       </c>
       <c r="Y15" s="1">
         <f t="shared" si="8"/>
-        <v>-6.515344959378111E-3</v>
+        <v>-4.4769874476987548E-3</v>
       </c>
       <c r="Z15" s="1">
         <f t="shared" si="8"/>
-        <v>1.739130434782607E-2</v>
-      </c>
-      <c r="AD15" s="10">
+        <v>-6.5217391304347838E-2</v>
+      </c>
+      <c r="AD15" s="7">
         <v>0.92531120331950212</v>
       </c>
       <c r="AE15" s="1">
@@ -2991,7 +2991,7 @@
       <c r="AF15" s="1">
         <v>0</v>
       </c>
-      <c r="AG15" s="10">
+      <c r="AG15" s="7">
         <v>0.38524520818669117</v>
       </c>
       <c r="AH15" s="1">
@@ -3006,23 +3006,23 @@
       </c>
       <c r="AM15" s="1">
         <f t="shared" ref="AM15:AQ15" si="9">B15-AE15</f>
-        <v>7.2176077294037078E-2</v>
+        <v>-4.6329714945620659E-2</v>
       </c>
       <c r="AN15" s="1">
         <f t="shared" si="9"/>
-        <v>1.0309278350515464E-2</v>
+        <v>0.38750000000000001</v>
       </c>
       <c r="AO15" s="3">
         <f t="shared" si="9"/>
-        <v>0.47926934304832958</v>
+        <v>0.48475479181330883</v>
       </c>
       <c r="AP15" s="1">
         <f t="shared" si="9"/>
-        <v>0.47805313924280868</v>
+        <v>0.48009149675448803</v>
       </c>
       <c r="AQ15" s="1">
         <f t="shared" si="9"/>
-        <v>0.21739130434782608</v>
+        <v>0.13478260869565217</v>
       </c>
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.3">
@@ -3040,31 +3040,31 @@
     </row>
     <row r="17" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <v>0.85771926098959439</v>
+        <v>0.86</v>
       </c>
       <c r="B17" s="1">
-        <v>0.99554345134934386</v>
+        <v>0.86</v>
       </c>
       <c r="C17" s="1">
-        <v>2.6865671641791045E-2</v>
+        <v>0.5</v>
       </c>
       <c r="D17" s="1">
-        <v>0.98777207141110301</v>
+        <v>0.98</v>
       </c>
       <c r="E17" s="1">
-        <v>0.98868945168428812</v>
+        <v>0.99</v>
       </c>
       <c r="F17" s="1">
-        <v>0.78260869565217395</v>
+        <v>0.54782608695652169</v>
       </c>
       <c r="L17">
         <v>0.86</v>
       </c>
       <c r="M17" s="1">
-        <v>0.99702307119821387</v>
+        <v>0.86041532862342107</v>
       </c>
       <c r="N17" s="1">
-        <v>2.2488755622188907E-2</v>
+        <v>0.55185185185185182</v>
       </c>
       <c r="O17" s="1">
         <v>0.99</v>
@@ -3073,33 +3073,33 @@
         <v>0.98917056362293876</v>
       </c>
       <c r="Q17" s="1">
-        <v>0.6</v>
+        <v>0.59599999999999997</v>
       </c>
       <c r="U17" s="3">
         <f>A17-L17</f>
-        <v>-2.2807390104055969E-3</v>
+        <v>0</v>
       </c>
       <c r="V17" s="1">
         <f t="shared" ref="V17:Z17" si="10">B17-M17</f>
-        <v>-1.4796198488700174E-3</v>
+        <v>-4.1532862342108512E-4</v>
       </c>
       <c r="W17" s="1">
         <f t="shared" si="10"/>
-        <v>4.3769160196021374E-3</v>
+        <v>-5.1851851851851816E-2</v>
       </c>
       <c r="X17" s="3">
         <f t="shared" si="10"/>
-        <v>-2.2279285888969769E-3</v>
+        <v>-1.0000000000000009E-2</v>
       </c>
       <c r="Y17" s="1">
         <f t="shared" si="10"/>
-        <v>-4.8111193865063573E-4</v>
+        <v>8.294363770612323E-4</v>
       </c>
       <c r="Z17" s="1">
         <f t="shared" si="10"/>
-        <v>0.18260869565217397</v>
-      </c>
-      <c r="AD17" s="10">
+        <v>-4.8173913043478289E-2</v>
+      </c>
+      <c r="AD17" s="7">
         <v>0.9015862738750402</v>
       </c>
       <c r="AE17" s="1">
@@ -3108,7 +3108,7 @@
       <c r="AF17" s="1">
         <v>0.25</v>
       </c>
-      <c r="AG17" s="10">
+      <c r="AG17" s="7">
         <v>0.68732088712359718</v>
       </c>
       <c r="AH17" s="1">
@@ -3119,27 +3119,27 @@
       </c>
       <c r="AL17" s="3">
         <f>A17-AD17</f>
-        <v>-4.3867012885445811E-2</v>
+        <v>-4.1586273875040214E-2</v>
       </c>
       <c r="AM17" s="1">
         <f t="shared" ref="AM17:AQ17" si="11">B17-AE17</f>
-        <v>9.311233303491917E-2</v>
+        <v>-4.2431118314424698E-2</v>
       </c>
       <c r="AN17" s="1">
         <f t="shared" si="11"/>
-        <v>-0.22313432835820896</v>
+        <v>0.25</v>
       </c>
       <c r="AO17" s="3">
         <f t="shared" si="11"/>
-        <v>0.30045118428750583</v>
+        <v>0.2926791128764028</v>
       </c>
       <c r="AP17" s="1">
         <f t="shared" si="11"/>
-        <v>0.29329850162951232</v>
+        <v>0.29460904994522419</v>
       </c>
       <c r="AQ17" s="1">
         <f t="shared" si="11"/>
-        <v>0.76096163682864448</v>
+        <v>0.52617902813299233</v>
       </c>
     </row>
   </sheetData>
